--- a/data/source/weekly/cs-en-us-pbqn.xlsx
+++ b/data/source/weekly/cs-en-us-pbqn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -873,10 +873,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K14" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="L14" s="15">
         <v>-50</v>
@@ -885,7 +885,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-93.333333333333</v>
+        <v>-95.238095238095</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D15" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>14.285714285714</v>
+        <v>300</v>
       </c>
       <c r="F15" s="14">
         <v>25</v>
       </c>
       <c r="G15" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H15" s="15">
-        <v>25</v>
+        <v>47.058823529411</v>
       </c>
       <c r="I15" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J15" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K15" s="15">
-        <v>20</v>
+        <v>30.769230769230</v>
       </c>
       <c r="L15" s="15">
-        <v>114.285714285714</v>
+        <v>126.666666666667</v>
       </c>
       <c r="M15" s="15">
         <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>36.363636363636</v>
+        <v>30.769230769230</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D16" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E16" s="15">
-        <v>57.142857142857</v>
+        <v>4.166666666666</v>
       </c>
       <c r="F16" s="14">
         <v>94</v>
       </c>
       <c r="G16" s="14">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H16" s="15">
-        <v>1.075268817204</v>
+        <v>2.173913043478</v>
       </c>
       <c r="I16" s="14">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="J16" s="14">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="K16" s="15">
-        <v>1.515151515151</v>
+        <v>1.923076923076</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.366515837104</v>
+        <v>-39.543726235741</v>
       </c>
       <c r="M16" s="15">
-        <v>-46.613545816733</v>
+        <v>-43.816254416961</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.276465441819</v>
+        <v>-87.890327494287</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" s="14">
         <v>49</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="F17" s="14">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="G17" s="14">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H17" s="15">
-        <v>-24.644549763033</v>
+        <v>-14.354066985645</v>
       </c>
       <c r="I17" s="14">
-        <v>238</v>
+        <v>289</v>
       </c>
       <c r="J17" s="14">
-        <v>305</v>
+        <v>354</v>
       </c>
       <c r="K17" s="15">
-        <v>-21.967213114754</v>
+        <v>-18.361581920904</v>
       </c>
       <c r="L17" s="15">
-        <v>-14.079422382671</v>
+        <v>-15</v>
       </c>
       <c r="M17" s="15">
-        <v>61.904761904761</v>
+        <v>74.096385542168</v>
       </c>
       <c r="N17" s="15">
-        <v>-10.861423220973</v>
+        <v>-7.371794871794</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D18" s="14">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E18" s="15">
-        <v>-35.897435897435</v>
+        <v>-68.085106382978</v>
       </c>
       <c r="F18" s="14">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G18" s="14">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="H18" s="15">
-        <v>-58.490566037735</v>
+        <v>-56.886227544910</v>
       </c>
       <c r="I18" s="14">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="J18" s="14">
-        <v>222</v>
+        <v>269</v>
       </c>
       <c r="K18" s="15">
-        <v>-51.801801801801</v>
+        <v>-53.903345724907</v>
       </c>
       <c r="L18" s="15">
-        <v>-49.289099526066</v>
+        <v>-51.181102362204</v>
       </c>
       <c r="M18" s="15">
-        <v>-67.076923076923</v>
+        <v>-66.576819407008</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.088397790055</v>
+        <v>-94.049904030710</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D19" s="14">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E19" s="15">
-        <v>-1.980198019801</v>
+        <v>-1.904761904761</v>
       </c>
       <c r="F19" s="14">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="G19" s="14">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H19" s="15">
-        <v>3.149606299212</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>580</v>
+        <v>687</v>
       </c>
       <c r="J19" s="14">
-        <v>523</v>
+        <v>628</v>
       </c>
       <c r="K19" s="15">
-        <v>10.898661567877</v>
+        <v>9.394904458598</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.280423280423</v>
+        <v>-20.578034682080</v>
       </c>
       <c r="M19" s="15">
-        <v>32.420091324200</v>
+        <v>39.634146341463</v>
       </c>
       <c r="N19" s="15">
-        <v>-28.834355828220</v>
+        <v>-28.881987577639</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D20" s="14">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E20" s="15">
-        <v>-17.142857142857</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G20" s="14">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H20" s="15">
-        <v>12.605042016806</v>
+        <v>15.384615384615</v>
       </c>
       <c r="I20" s="14">
-        <v>192</v>
+        <v>231</v>
       </c>
       <c r="J20" s="14">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="K20" s="15">
-        <v>6.077348066298</v>
+        <v>14.925373134328</v>
       </c>
       <c r="L20" s="15">
-        <v>-19.665271966527</v>
+        <v>-15.693430656934</v>
       </c>
       <c r="M20" s="15">
-        <v>7.262569832402</v>
+        <v>17.258883248731</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.038433647570</v>
+        <v>-92.724409448818</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D21" s="17">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E21" s="18">
-        <v>-3.952569169960</v>
+        <v>-4.858299595141</v>
       </c>
       <c r="F21" s="17">
-        <v>872</v>
+        <v>892</v>
       </c>
       <c r="G21" s="17">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.651469098277</v>
+        <v>-10.080645161290</v>
       </c>
       <c r="I21" s="17">
-        <v>1282</v>
+        <v>1525</v>
       </c>
       <c r="J21" s="17">
-        <v>1392</v>
+        <v>1639</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.902298850574</v>
+        <v>-6.955460646735</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.465116279069</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="M21" s="18">
-        <v>-5.596465390279</v>
+        <v>-0.261608894702</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.229868228404</v>
+        <v>-80.688869190832</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>28</v>
       </c>
       <c r="C22" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D22" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E22" s="15">
-        <v>225</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F22" s="14">
         <v>28</v>
       </c>
       <c r="G22" s="14">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H22" s="15">
-        <v>75</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J22" s="14">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="K22" s="15">
-        <v>37.5</v>
+        <v>8.571428571428</v>
       </c>
       <c r="L22" s="15">
-        <v>22.222222222222</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M22" s="15">
-        <v>32</v>
+        <v>31.034482758620</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>29</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F23" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G23" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" s="15">
-        <v>-18.75</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="I23" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J23" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K23" s="15">
-        <v>-20.833333333333</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="L23" s="15">
-        <v>18.75</v>
+        <v>4.545454545454</v>
       </c>
       <c r="M23" s="15">
-        <v>18.75</v>
+        <v>15</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>29</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="D24" s="14">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="E24" s="15">
-        <v>-28.308823529411</v>
+        <v>-13.120567375886</v>
       </c>
       <c r="F24" s="14">
-        <v>964</v>
+        <v>930</v>
       </c>
       <c r="G24" s="14">
-        <v>1092</v>
+        <v>1117</v>
       </c>
       <c r="H24" s="15">
-        <v>-11.721611721611</v>
+        <v>-16.741271262309</v>
       </c>
       <c r="I24" s="14">
-        <v>1361</v>
+        <v>1605</v>
       </c>
       <c r="J24" s="14">
-        <v>1474</v>
+        <v>1756</v>
       </c>
       <c r="K24" s="15">
-        <v>-7.666214382632</v>
+        <v>-8.599088838268</v>
       </c>
       <c r="L24" s="15">
-        <v>-25.628415300546</v>
+        <v>-25.694444444444</v>
       </c>
       <c r="M24" s="15">
-        <v>45.873526259378</v>
+        <v>53.002859866539</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>29</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="D25" s="14">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="E25" s="15">
-        <v>-40</v>
+        <v>-20.224719101123</v>
       </c>
       <c r="F25" s="14">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="G25" s="14">
-        <v>653</v>
+        <v>669</v>
       </c>
       <c r="H25" s="15">
-        <v>-22.511485451761</v>
+        <v>-23.168908819133</v>
       </c>
       <c r="I25" s="14">
-        <v>663</v>
+        <v>804</v>
       </c>
       <c r="J25" s="14">
-        <v>890</v>
+        <v>1068</v>
       </c>
       <c r="K25" s="15">
-        <v>-25.505617977528</v>
+        <v>-24.719101123595</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.891205802357</v>
+        <v>-38.859315589353</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>29</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D26" s="14">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E26" s="15">
-        <v>17.721518987341</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="G26" s="14">
-        <v>366</v>
+        <v>338</v>
       </c>
       <c r="H26" s="15">
-        <v>-6.010928961748</v>
+        <v>7.396449704142</v>
       </c>
       <c r="I26" s="14">
-        <v>506</v>
+        <v>608</v>
       </c>
       <c r="J26" s="14">
-        <v>514</v>
+        <v>604</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.556420233463</v>
+        <v>0.662251655629</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.393700787401</v>
+        <v>-2.875399361022</v>
       </c>
       <c r="M26" s="15">
-        <v>7.659574468085</v>
+        <v>9.156193895870</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>29</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D27" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F27" s="14">
         <v>30</v>
       </c>
       <c r="G27" s="14">
+        <v>24</v>
+      </c>
+      <c r="H27" s="15">
         <v>25</v>
       </c>
-      <c r="H27" s="15">
-        <v>20</v>
-      </c>
       <c r="I27" s="14">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J27" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K27" s="15">
-        <v>12.121212121212</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>48</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>29</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D28" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E28" s="15">
-        <v>16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F28" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G28" s="14">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H28" s="15">
-        <v>-34.042553191489</v>
+        <v>-25.581395348837</v>
       </c>
       <c r="I28" s="14">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J28" s="14">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K28" s="15">
-        <v>-26.666666666666</v>
+        <v>-23.880597014925</v>
       </c>
       <c r="L28" s="15">
-        <v>-26.666666666666</v>
+        <v>-28.169014084507</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>29</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>29</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29" s="15">
+        <v>-60</v>
+      </c>
+      <c r="L29" s="15">
+        <v>0</v>
+      </c>
+      <c r="M29" s="15">
         <v>-50</v>
       </c>
-      <c r="L29" s="15">
-        <v>100</v>
-      </c>
-      <c r="M29" s="15">
-        <v>-33.333333333333</v>
-      </c>
       <c r="N29" s="15">
-        <v>-94.117647058823</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>29</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="L30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.117647058823</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1549,34 +1549,34 @@
         <v>38</v>
       </c>
       <c r="C31" s="14">
-        <v>1</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>29</v>
+        <v>2</v>
+      </c>
+      <c r="D31" s="14">
+        <v>3</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F31" s="14">
+        <v>7</v>
+      </c>
+      <c r="G31" s="14">
         <v>5</v>
       </c>
-      <c r="G31" s="14">
-        <v>3</v>
-      </c>
       <c r="H31" s="15">
-        <v>66.666666666666</v>
+        <v>40</v>
       </c>
       <c r="I31" s="14">
+        <v>10</v>
+      </c>
+      <c r="J31" s="14">
         <v>7</v>
       </c>
-      <c r="J31" s="14">
-        <v>4</v>
-      </c>
       <c r="K31" s="15">
-        <v>75</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L31" s="15">
-        <v>-22.222222222222</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>29</v>
@@ -1607,35 +1607,35 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>2</v>
-      </c>
-      <c r="D33" s="13" t="s">
+      <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="13" t="s">
-        <v>29</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
         <v>3</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>29</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>200</v>
       </c>
       <c r="I33" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L33" s="15">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>29</v>

--- a/data/source/weekly/cs-en-us-pbqn.xlsx
+++ b/data/source/weekly/cs-en-us-pbqn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,20 +854,20 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="14">
+        <v>3</v>
+      </c>
+      <c r="H14" s="15">
         <v>-100</v>
-      </c>
-      <c r="F14" s="14">
-        <v>1</v>
-      </c>
-      <c r="G14" s="14">
-        <v>4</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-75</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -882,338 +882,338 @@
         <v>-50</v>
       </c>
       <c r="M14" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N14" s="15">
-        <v>-95.238095238095</v>
+        <v>-95.652173913043</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E15" s="15">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="F15" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G15" s="14">
         <v>17</v>
       </c>
       <c r="H15" s="15">
-        <v>47.058823529411</v>
+        <v>41.176470588235</v>
       </c>
       <c r="I15" s="14">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J15" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K15" s="15">
-        <v>30.769230769230</v>
+        <v>32.258064516129</v>
       </c>
       <c r="L15" s="15">
-        <v>126.666666666667</v>
+        <v>105</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>141.176470588235</v>
       </c>
       <c r="N15" s="15">
-        <v>30.769230769230</v>
+        <v>46.428571428571</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D16" s="14">
         <v>24</v>
       </c>
       <c r="E16" s="15">
-        <v>4.166666666666</v>
+        <v>41.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="G16" s="14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H16" s="15">
-        <v>2.173913043478</v>
+        <v>11.458333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="J16" s="14">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="K16" s="15">
-        <v>1.923076923076</v>
+        <v>7.222222222222</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.543726235741</v>
+        <v>-36.721311475409</v>
       </c>
       <c r="M16" s="15">
-        <v>-43.816254416961</v>
+        <v>-37.942122186495</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.890327494287</v>
+        <v>-86.834924965893</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
         <v>48</v>
       </c>
       <c r="D17" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E17" s="15">
-        <v>-2.040816326530</v>
+        <v>-12.727272727272</v>
       </c>
       <c r="F17" s="14">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G17" s="14">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H17" s="15">
-        <v>-14.354066985645</v>
+        <v>-8.173076923076</v>
       </c>
       <c r="I17" s="14">
-        <v>289</v>
+        <v>339</v>
       </c>
       <c r="J17" s="14">
-        <v>354</v>
+        <v>409</v>
       </c>
       <c r="K17" s="15">
-        <v>-18.361581920904</v>
+        <v>-17.114914425427</v>
       </c>
       <c r="L17" s="15">
-        <v>-15</v>
+        <v>-14.609571788413</v>
       </c>
       <c r="M17" s="15">
-        <v>74.096385542168</v>
+        <v>83.243243243243</v>
       </c>
       <c r="N17" s="15">
-        <v>-7.371794871794</v>
+        <v>-4.775280898876</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D18" s="14">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="E18" s="15">
-        <v>-68.085106382978</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F18" s="14">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="G18" s="14">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="H18" s="15">
-        <v>-56.886227544910</v>
+        <v>-44.155844155844</v>
       </c>
       <c r="I18" s="14">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="J18" s="14">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="K18" s="15">
-        <v>-53.903345724907</v>
+        <v>-46.779661016949</v>
       </c>
       <c r="L18" s="15">
-        <v>-51.181102362204</v>
+        <v>-46.598639455782</v>
       </c>
       <c r="M18" s="15">
-        <v>-66.576819407008</v>
+        <v>-64.155251141552</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.049904030710</v>
+        <v>-93.372731110173</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D19" s="14">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="E19" s="15">
-        <v>-1.904761904761</v>
+        <v>20.689655172413</v>
       </c>
       <c r="F19" s="14">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="G19" s="14">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>-0.763358778625</v>
       </c>
       <c r="I19" s="14">
-        <v>687</v>
+        <v>791</v>
       </c>
       <c r="J19" s="14">
-        <v>628</v>
+        <v>715</v>
       </c>
       <c r="K19" s="15">
-        <v>9.394904458598</v>
+        <v>10.629370629370</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.578034682080</v>
+        <v>-20.181634712411</v>
       </c>
       <c r="M19" s="15">
-        <v>39.634146341463</v>
+        <v>41.756272401433</v>
       </c>
       <c r="N19" s="15">
-        <v>-28.881987577639</v>
+        <v>-27.696526508226</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D20" s="14">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>43.243243243243</v>
       </c>
       <c r="F20" s="14">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G20" s="14">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H20" s="15">
-        <v>15.384615384615</v>
+        <v>10</v>
       </c>
       <c r="I20" s="14">
-        <v>231</v>
+        <v>283</v>
       </c>
       <c r="J20" s="14">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="K20" s="15">
-        <v>14.925373134328</v>
+        <v>18.907563025210</v>
       </c>
       <c r="L20" s="15">
-        <v>-15.693430656934</v>
+        <v>-7.213114754098</v>
       </c>
       <c r="M20" s="15">
-        <v>17.258883248731</v>
+        <v>25.777777777777</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.724409448818</v>
+        <v>-92.141071924465</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>235</v>
+        <v>279</v>
       </c>
       <c r="D21" s="17">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="E21" s="18">
-        <v>-4.858299595141</v>
+        <v>19.230769230769</v>
       </c>
       <c r="F21" s="17">
-        <v>892</v>
+        <v>930</v>
       </c>
       <c r="G21" s="17">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.080645161290</v>
+        <v>-6.155398587285</v>
       </c>
       <c r="I21" s="17">
-        <v>1525</v>
+        <v>1805</v>
       </c>
       <c r="J21" s="17">
-        <v>1639</v>
+        <v>1873</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.955460646735</v>
+        <v>-3.630539241857</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.242424242424</v>
+        <v>-21.996542783059</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.261608894702</v>
+        <v>3.855005753739</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.688869190832</v>
+        <v>-79.803065905784</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
         <v>5</v>
       </c>
       <c r="D22" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>-54.545454545454</v>
+        <v>25</v>
       </c>
       <c r="F22" s="14">
         <v>28</v>
       </c>
       <c r="G22" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H22" s="15">
-        <v>16.666666666666</v>
+        <v>21.739130434782</v>
       </c>
       <c r="I22" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J22" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K22" s="15">
-        <v>8.571428571428</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L22" s="15">
-        <v>11.764705882352</v>
+        <v>13.513513513513</v>
       </c>
       <c r="M22" s="15">
-        <v>31.034482758620</v>
+        <v>40</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1224,37 +1224,37 @@
         <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E23" s="15">
-        <v>-20</v>
+        <v>-60</v>
       </c>
       <c r="F23" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G23" s="14">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H23" s="15">
-        <v>-17.647058823529</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="I23" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J23" s="14">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K23" s="15">
-        <v>-20.689655172413</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="L23" s="15">
-        <v>4.545454545454</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="M23" s="15">
-        <v>15</v>
+        <v>17.391304347826</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="D24" s="14">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E24" s="15">
-        <v>-13.120567375886</v>
+        <v>-18.021201413427</v>
       </c>
       <c r="F24" s="14">
-        <v>930</v>
+        <v>880</v>
       </c>
       <c r="G24" s="14">
-        <v>1117</v>
+        <v>1107</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.741271262309</v>
+        <v>-20.505871725383</v>
       </c>
       <c r="I24" s="14">
-        <v>1605</v>
+        <v>1832</v>
       </c>
       <c r="J24" s="14">
-        <v>1756</v>
+        <v>2039</v>
       </c>
       <c r="K24" s="15">
-        <v>-8.599088838268</v>
+        <v>-10.152035311427</v>
       </c>
       <c r="L24" s="15">
-        <v>-25.694444444444</v>
+        <v>-26.866267465069</v>
       </c>
       <c r="M24" s="15">
-        <v>53.002859866539</v>
+        <v>54.079058031959</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D25" s="14">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="E25" s="15">
-        <v>-20.224719101123</v>
+        <v>-24.352331606217</v>
       </c>
       <c r="F25" s="14">
         <v>514</v>
       </c>
       <c r="G25" s="14">
-        <v>669</v>
+        <v>692</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.168908819133</v>
+        <v>-25.722543352601</v>
       </c>
       <c r="I25" s="14">
-        <v>804</v>
+        <v>948</v>
       </c>
       <c r="J25" s="14">
-        <v>1068</v>
+        <v>1261</v>
       </c>
       <c r="K25" s="15">
-        <v>-24.719101123595</v>
+        <v>-24.821570182394</v>
       </c>
       <c r="L25" s="15">
-        <v>-38.859315589353</v>
+        <v>-37.549407114624</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D26" s="14">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E26" s="15">
-        <v>16.666666666666</v>
+        <v>17.283950617283</v>
       </c>
       <c r="F26" s="14">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="G26" s="14">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="H26" s="15">
-        <v>7.396449704142</v>
+        <v>9.275362318840</v>
       </c>
       <c r="I26" s="14">
-        <v>608</v>
+        <v>700</v>
       </c>
       <c r="J26" s="14">
-        <v>604</v>
+        <v>685</v>
       </c>
       <c r="K26" s="15">
-        <v>0.662251655629</v>
+        <v>2.189781021897</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.875399361022</v>
+        <v>-8.015768725361</v>
       </c>
       <c r="M26" s="15">
-        <v>9.156193895870</v>
+        <v>9.034267912772</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G27" s="14">
         <v>24</v>
       </c>
       <c r="H27" s="15">
-        <v>25</v>
+        <v>20.833333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J27" s="14">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K27" s="15">
-        <v>16.666666666666</v>
+        <v>13.953488372093</v>
       </c>
       <c r="L27" s="15">
-        <v>55.555555555555</v>
+        <v>48.484848484848</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,122 +1426,122 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E28" s="15">
-        <v>-14.285714285714</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F28" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G28" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H28" s="15">
-        <v>-25.581395348837</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="I28" s="14">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J28" s="14">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="K28" s="15">
-        <v>-23.880597014925</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="L28" s="15">
-        <v>-28.169014084507</v>
+        <v>-28.75</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>4</v>
       </c>
       <c r="D29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H29" s="15">
-        <v>-75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J29" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>-60</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L29" s="15">
+        <v>200</v>
+      </c>
+      <c r="M29" s="15">
         <v>0</v>
       </c>
-      <c r="M29" s="15">
-        <v>-50</v>
-      </c>
       <c r="N29" s="15">
-        <v>-95</v>
+        <v>-86.956521739130</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="14">
+        <v>4</v>
+      </c>
+      <c r="D30" s="14">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>100</v>
+      </c>
+      <c r="F30" s="14">
+        <v>4</v>
+      </c>
+      <c r="G30" s="14">
+        <v>6</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="I30" s="14">
+        <v>6</v>
+      </c>
+      <c r="J30" s="14">
+        <v>7</v>
+      </c>
+      <c r="K30" s="15">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="L30" s="15">
+        <v>200</v>
+      </c>
+      <c r="M30" s="15">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="14">
-        <v>1</v>
-      </c>
-      <c r="G30" s="14">
-        <v>4</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-75</v>
-      </c>
-      <c r="I30" s="14">
-        <v>2</v>
-      </c>
-      <c r="J30" s="14">
-        <v>5</v>
-      </c>
-      <c r="K30" s="15">
-        <v>-60</v>
-      </c>
-      <c r="L30" s="15">
-        <v>0</v>
-      </c>
-      <c r="M30" s="15">
-        <v>-33.333333333333</v>
-      </c>
       <c r="N30" s="15">
-        <v>-95</v>
+        <v>-86.956521739130</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,38 +1551,38 @@
       <c r="C31" s="14">
         <v>2</v>
       </c>
-      <c r="D31" s="14">
-        <v>3</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-33.333333333333</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G31" s="14">
+        <v>4</v>
+      </c>
+      <c r="H31" s="15">
+        <v>150</v>
+      </c>
+      <c r="I31" s="14">
+        <v>14</v>
+      </c>
+      <c r="J31" s="14">
         <v>5</v>
       </c>
-      <c r="H31" s="15">
+      <c r="K31" s="15">
+        <v>180</v>
+      </c>
+      <c r="L31" s="15">
         <v>40</v>
       </c>
-      <c r="I31" s="14">
-        <v>10</v>
-      </c>
-      <c r="J31" s="14">
-        <v>7</v>
-      </c>
-      <c r="K31" s="15">
-        <v>42.857142857142</v>
-      </c>
-      <c r="L31" s="15">
-        <v>0</v>
-      </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1610,20 +1610,20 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I33" s="14">
         <v>5</v>
@@ -1635,13 +1635,13 @@
         <v>150</v>
       </c>
       <c r="L33" s="15">
-        <v>-44.444444444444</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>218</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>10079</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>2992</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>17454</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>11614</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>28509</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>71017</v>

--- a/data/source/weekly/cs-en-us-pbqn.xlsx
+++ b/data/source/weekly/cs-en-us-pbqn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -864,7 +864,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F15" s="14">
         <v>24</v>
       </c>
       <c r="G15" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H15" s="15">
-        <v>41.176470588235</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J15" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K15" s="15">
-        <v>32.258064516129</v>
+        <v>32.352941176470</v>
       </c>
       <c r="L15" s="15">
-        <v>105</v>
+        <v>73.076923076923</v>
       </c>
       <c r="M15" s="15">
-        <v>141.176470588235</v>
+        <v>150</v>
       </c>
       <c r="N15" s="15">
-        <v>46.428571428571</v>
+        <v>36.363636363636</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D16" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E16" s="15">
-        <v>41.666666666666</v>
+        <v>-12</v>
       </c>
       <c r="F16" s="14">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G16" s="14">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H16" s="15">
-        <v>11.458333333333</v>
+        <v>21.276595744680</v>
       </c>
       <c r="I16" s="14">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="J16" s="14">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="K16" s="15">
-        <v>7.222222222222</v>
+        <v>5.365853658536</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.721311475409</v>
+        <v>-39.325842696629</v>
       </c>
       <c r="M16" s="15">
-        <v>-37.942122186495</v>
+        <v>-36.094674556213</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.834924965893</v>
+        <v>-86.772810777709</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D17" s="14">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="E17" s="15">
-        <v>-12.727272727272</v>
+        <v>-19.178082191780</v>
       </c>
       <c r="F17" s="14">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="G17" s="14">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="H17" s="15">
-        <v>-8.173076923076</v>
+        <v>-9.292035398230</v>
       </c>
       <c r="I17" s="14">
-        <v>339</v>
+        <v>400</v>
       </c>
       <c r="J17" s="14">
-        <v>409</v>
+        <v>482</v>
       </c>
       <c r="K17" s="15">
-        <v>-17.114914425427</v>
+        <v>-17.012448132780</v>
       </c>
       <c r="L17" s="15">
-        <v>-14.609571788413</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M17" s="15">
-        <v>83.243243243243</v>
+        <v>94.174757281553</v>
       </c>
       <c r="N17" s="15">
-        <v>-4.775280898876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D18" s="14">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E18" s="15">
-        <v>23.076923076923</v>
+        <v>-37.209302325581</v>
       </c>
       <c r="F18" s="14">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="G18" s="14">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H18" s="15">
-        <v>-44.155844155844</v>
+        <v>-36.129032258064</v>
       </c>
       <c r="I18" s="14">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="J18" s="14">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="K18" s="15">
-        <v>-46.779661016949</v>
+        <v>-45.562130177514</v>
       </c>
       <c r="L18" s="15">
-        <v>-46.598639455782</v>
+        <v>-46.974063400576</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.155251141552</v>
+        <v>-62.448979591836</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.372731110173</v>
+        <v>-93.038214150586</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D19" s="14">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E19" s="15">
-        <v>20.689655172413</v>
+        <v>-9</v>
       </c>
       <c r="F19" s="14">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="G19" s="14">
         <v>393</v>
       </c>
       <c r="H19" s="15">
-        <v>-0.763358778625</v>
+        <v>0.763358778625</v>
       </c>
       <c r="I19" s="14">
-        <v>791</v>
+        <v>882</v>
       </c>
       <c r="J19" s="14">
-        <v>715</v>
+        <v>815</v>
       </c>
       <c r="K19" s="15">
-        <v>10.629370629370</v>
+        <v>8.220858895705</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.181634712411</v>
+        <v>-22.427440633245</v>
       </c>
       <c r="M19" s="15">
-        <v>41.756272401433</v>
+        <v>45.304777594728</v>
       </c>
       <c r="N19" s="15">
-        <v>-27.696526508226</v>
+        <v>-29.099678456591</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D20" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E20" s="15">
-        <v>43.243243243243</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="F20" s="14">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="G20" s="14">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="H20" s="15">
-        <v>10</v>
+        <v>16.793893129771</v>
       </c>
       <c r="I20" s="14">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="J20" s="14">
-        <v>238</v>
+        <v>277</v>
       </c>
       <c r="K20" s="15">
-        <v>18.907563025210</v>
+        <v>14.440433212996</v>
       </c>
       <c r="L20" s="15">
-        <v>-7.213114754098</v>
+        <v>-9.428571428571</v>
       </c>
       <c r="M20" s="15">
-        <v>25.777777777777</v>
+        <v>23.346303501945</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.141071924465</v>
+        <v>-92.110502737680</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>279</v>
+        <v>239</v>
       </c>
       <c r="D21" s="17">
-        <v>234</v>
+        <v>283</v>
       </c>
       <c r="E21" s="18">
-        <v>19.230769230769</v>
+        <v>-15.547703180212</v>
       </c>
       <c r="F21" s="17">
-        <v>930</v>
+        <v>991</v>
       </c>
       <c r="G21" s="17">
-        <v>991</v>
+        <v>1017</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.155398587285</v>
+        <v>-2.556538839724</v>
       </c>
       <c r="I21" s="17">
-        <v>1805</v>
+        <v>2045</v>
       </c>
       <c r="J21" s="17">
-        <v>1873</v>
+        <v>2156</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.630539241857</v>
+        <v>-5.148423005565</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.996542783059</v>
+        <v>-23.350824587706</v>
       </c>
       <c r="M21" s="18">
-        <v>3.855005753739</v>
+        <v>6.510416666666</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.803065905784</v>
+        <v>-79.537722633580</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" s="15">
-        <v>25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F22" s="14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G22" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H22" s="15">
-        <v>21.739130434782</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I22" s="14">
+        <v>44</v>
+      </c>
+      <c r="J22" s="14">
         <v>42</v>
       </c>
-      <c r="J22" s="14">
-        <v>39</v>
-      </c>
       <c r="K22" s="15">
-        <v>7.692307692307</v>
+        <v>4.761904761904</v>
       </c>
       <c r="L22" s="15">
-        <v>13.513513513513</v>
+        <v>4.761904761904</v>
       </c>
       <c r="M22" s="15">
-        <v>40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" s="14">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-60</v>
+        <v>400</v>
       </c>
       <c r="F23" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G23" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H23" s="15">
-        <v>-42.307692307692</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I23" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J23" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K23" s="15">
-        <v>-30.769230769230</v>
+        <v>-20</v>
       </c>
       <c r="L23" s="15">
-        <v>-22.857142857142</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="M23" s="15">
-        <v>17.391304347826</v>
+        <v>18.518518518518</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="D24" s="14">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E24" s="15">
-        <v>-18.021201413427</v>
+        <v>-24.452554744525</v>
       </c>
       <c r="F24" s="14">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G24" s="14">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="H24" s="15">
-        <v>-20.505871725383</v>
+        <v>-21.242124212421</v>
       </c>
       <c r="I24" s="14">
-        <v>1832</v>
+        <v>2034</v>
       </c>
       <c r="J24" s="14">
-        <v>2039</v>
+        <v>2313</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.152035311427</v>
+        <v>-12.062256809338</v>
       </c>
       <c r="L24" s="15">
-        <v>-26.866267465069</v>
+        <v>-30.175077239958</v>
       </c>
       <c r="M24" s="15">
-        <v>54.079058031959</v>
+        <v>54.676806083650</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="D25" s="14">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="E25" s="15">
-        <v>-24.352331606217</v>
+        <v>-42.458100558659</v>
       </c>
       <c r="F25" s="14">
-        <v>514</v>
+        <v>481</v>
       </c>
       <c r="G25" s="14">
-        <v>692</v>
+        <v>710</v>
       </c>
       <c r="H25" s="15">
-        <v>-25.722543352601</v>
+        <v>-32.253521126760</v>
       </c>
       <c r="I25" s="14">
-        <v>948</v>
+        <v>1048</v>
       </c>
       <c r="J25" s="14">
-        <v>1261</v>
+        <v>1440</v>
       </c>
       <c r="K25" s="15">
-        <v>-24.821570182394</v>
+        <v>-27.222222222222</v>
       </c>
       <c r="L25" s="15">
-        <v>-37.549407114624</v>
+        <v>-41.419787590832</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D26" s="14">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="E26" s="15">
-        <v>17.283950617283</v>
+        <v>-20.202020202020</v>
       </c>
       <c r="F26" s="14">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="G26" s="14">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H26" s="15">
-        <v>9.275362318840</v>
+        <v>6.590257879656</v>
       </c>
       <c r="I26" s="14">
-        <v>700</v>
+        <v>779</v>
       </c>
       <c r="J26" s="14">
-        <v>685</v>
+        <v>784</v>
       </c>
       <c r="K26" s="15">
-        <v>2.189781021897</v>
+        <v>-0.637755102040</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.015768725361</v>
+        <v>-12.076749435665</v>
       </c>
       <c r="M26" s="15">
-        <v>9.034267912772</v>
+        <v>6.275579809004</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F27" s="14">
         <v>29</v>
       </c>
       <c r="G27" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H27" s="15">
-        <v>20.833333333333</v>
+        <v>38.095238095238</v>
       </c>
       <c r="I27" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J27" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K27" s="15">
-        <v>13.953488372093</v>
+        <v>17.391304347826</v>
       </c>
       <c r="L27" s="15">
-        <v>48.484848484848</v>
+        <v>38.461538461538</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E28" s="15">
-        <v>-36.363636363636</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F28" s="14">
         <v>36</v>
       </c>
       <c r="G28" s="14">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H28" s="15">
-        <v>-23.404255319148</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I28" s="14">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="J28" s="14">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K28" s="15">
-        <v>-26.923076923076</v>
+        <v>-24.444444444444</v>
       </c>
       <c r="L28" s="15">
-        <v>-28.75</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,117 +1466,117 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>4</v>
-      </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>100</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J29" s="14">
         <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>-14.285714285714</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L29" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N29" s="15">
-        <v>-86.956521739130</v>
+        <v>-89.583333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>4</v>
-      </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
-      <c r="E30" s="15">
-        <v>100</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J30" s="14">
         <v>7</v>
       </c>
       <c r="K30" s="15">
-        <v>-14.285714285714</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L30" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="M30" s="15">
-        <v>20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-86.956521739130</v>
+        <v>-89.583333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>2</v>
-      </c>
-      <c r="D31" s="13" t="s">
+      <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>3</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G31" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H31" s="15">
-        <v>150</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I31" s="14">
         <v>14</v>
       </c>
       <c r="J31" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K31" s="15">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="L31" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
         <v>2</v>
       </c>
       <c r="G33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14">
         <v>5</v>
       </c>
       <c r="J33" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L33" s="15">
         <v>-54.545454545454</v>

--- a/data/source/weekly/cs-en-us-pbqn.xlsx
+++ b/data/source/weekly/cs-en-us-pbqn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,32 +860,32 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0</v>
+      </c>
+      <c r="I14" s="14">
         <v>2</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I14" s="14">
-        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>5</v>
       </c>
       <c r="K14" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="L14" s="15">
+        <v>0</v>
+      </c>
+      <c r="M14" s="15">
         <v>-50</v>
       </c>
-      <c r="M14" s="15">
-        <v>-75</v>
-      </c>
       <c r="N14" s="15">
-        <v>-95.652173913043</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="15">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="F15" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G15" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H15" s="15">
+        <v>61.538461538461</v>
+      </c>
+      <c r="I15" s="14">
         <v>50</v>
       </c>
-      <c r="I15" s="14">
-        <v>45</v>
-      </c>
       <c r="J15" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K15" s="15">
-        <v>32.352941176470</v>
+        <v>31.578947368421</v>
       </c>
       <c r="L15" s="15">
-        <v>73.076923076923</v>
+        <v>72.413793103448</v>
       </c>
       <c r="M15" s="15">
-        <v>150</v>
+        <v>138.095238095238</v>
       </c>
       <c r="N15" s="15">
-        <v>36.363636363636</v>
+        <v>51.515151515151</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E16" s="15">
-        <v>-12</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="G16" s="14">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H16" s="15">
-        <v>21.276595744680</v>
+        <v>5.154639175257</v>
       </c>
       <c r="I16" s="14">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="J16" s="14">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="K16" s="15">
-        <v>5.365853658536</v>
+        <v>3.493449781659</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.325842696629</v>
+        <v>-39.386189258312</v>
       </c>
       <c r="M16" s="15">
-        <v>-36.094674556213</v>
+        <v>-34.890109890109</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.772810777709</v>
+        <v>-86.647887323943</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D17" s="14">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E17" s="15">
-        <v>-19.178082191780</v>
+        <v>-24.528301886792</v>
       </c>
       <c r="F17" s="14">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="G17" s="14">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H17" s="15">
-        <v>-9.292035398230</v>
+        <v>-13.478260869565</v>
       </c>
       <c r="I17" s="14">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="J17" s="14">
-        <v>482</v>
+        <v>535</v>
       </c>
       <c r="K17" s="15">
-        <v>-17.012448132780</v>
+        <v>-16.635514018691</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.111111111111</v>
+        <v>-11.507936507936</v>
       </c>
       <c r="M17" s="15">
-        <v>94.174757281553</v>
+        <v>92.241379310344</v>
       </c>
       <c r="N17" s="15">
-        <v>0</v>
+        <v>-1.108647450110</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D18" s="14">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E18" s="15">
-        <v>-37.209302325581</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="F18" s="14">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G18" s="14">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H18" s="15">
-        <v>-36.129032258064</v>
+        <v>-34.415584415584</v>
       </c>
       <c r="I18" s="14">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="J18" s="14">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="K18" s="15">
-        <v>-45.562130177514</v>
+        <v>-43.085106382978</v>
       </c>
       <c r="L18" s="15">
-        <v>-46.974063400576</v>
+        <v>-44.702842377261</v>
       </c>
       <c r="M18" s="15">
-        <v>-62.448979591836</v>
+        <v>-60.948905109489</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.038214150586</v>
+        <v>-92.718611772711</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="D19" s="14">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="E19" s="15">
-        <v>-9</v>
+        <v>-12.096774193548</v>
       </c>
       <c r="F19" s="14">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="G19" s="14">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="H19" s="15">
-        <v>0.763358778625</v>
+        <v>-2.163461538461</v>
       </c>
       <c r="I19" s="14">
-        <v>882</v>
+        <v>995</v>
       </c>
       <c r="J19" s="14">
-        <v>815</v>
+        <v>939</v>
       </c>
       <c r="K19" s="15">
-        <v>8.220858895705</v>
+        <v>5.963791267305</v>
       </c>
       <c r="L19" s="15">
-        <v>-22.427440633245</v>
+        <v>-20.463629096722</v>
       </c>
       <c r="M19" s="15">
-        <v>45.304777594728</v>
+        <v>45.894428152492</v>
       </c>
       <c r="N19" s="15">
-        <v>-29.099678456591</v>
+        <v>-28.468727534148</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D20" s="14">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E20" s="15">
-        <v>-12.820512820512</v>
+        <v>29.729729729729</v>
       </c>
       <c r="F20" s="14">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="G20" s="14">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H20" s="15">
-        <v>16.793893129771</v>
+        <v>29.323308270676</v>
       </c>
       <c r="I20" s="14">
-        <v>317</v>
+        <v>364</v>
       </c>
       <c r="J20" s="14">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="K20" s="15">
-        <v>14.440433212996</v>
+        <v>15.923566878980</v>
       </c>
       <c r="L20" s="15">
-        <v>-9.428571428571</v>
+        <v>-7.614213197969</v>
       </c>
       <c r="M20" s="15">
-        <v>23.346303501945</v>
+        <v>24.232081911262</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.110502737680</v>
+        <v>-91.809180918091</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D21" s="17">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.547703180212</v>
+        <v>-11.785714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>991</v>
+        <v>1003</v>
       </c>
       <c r="G21" s="17">
-        <v>1017</v>
+        <v>1044</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.556538839724</v>
+        <v>-3.927203065134</v>
       </c>
       <c r="I21" s="17">
-        <v>2045</v>
+        <v>2308</v>
       </c>
       <c r="J21" s="17">
-        <v>2156</v>
+        <v>2436</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.148423005565</v>
+        <v>-5.254515599343</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.350824587706</v>
+        <v>-21.974306964165</v>
       </c>
       <c r="M21" s="18">
-        <v>6.510416666666</v>
+        <v>7.649253731343</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.537722633580</v>
+        <v>-79.133893861314</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E22" s="15">
-        <v>-33.333333333333</v>
+        <v>-62.5</v>
       </c>
       <c r="F22" s="14">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G22" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H22" s="15">
-        <v>9.090909090909</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I22" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J22" s="14">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="K22" s="15">
-        <v>4.761904761904</v>
+        <v>-8</v>
       </c>
       <c r="L22" s="15">
-        <v>4.761904761904</v>
+        <v>-9.803921568627</v>
       </c>
       <c r="M22" s="15">
-        <v>33.333333333333</v>
+        <v>17.948717948717</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>4</v>
+      </c>
+      <c r="D23" s="14">
         <v>5</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
       <c r="E23" s="15">
-        <v>400</v>
+        <v>-20</v>
       </c>
       <c r="F23" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G23" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H23" s="15">
-        <v>-27.272727272727</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I23" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J23" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K23" s="15">
-        <v>-20</v>
+        <v>-17.777777777777</v>
       </c>
       <c r="L23" s="15">
-        <v>-23.809523809523</v>
+        <v>-17.777777777777</v>
       </c>
       <c r="M23" s="15">
-        <v>18.518518518518</v>
+        <v>27.586206896551</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>207</v>
+        <v>277</v>
       </c>
       <c r="D24" s="14">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E24" s="15">
-        <v>-24.452554744525</v>
+        <v>2.592592592592</v>
       </c>
       <c r="F24" s="14">
-        <v>875</v>
+        <v>948</v>
       </c>
       <c r="G24" s="14">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="H24" s="15">
-        <v>-21.242124212421</v>
+        <v>-14.517583408476</v>
       </c>
       <c r="I24" s="14">
-        <v>2034</v>
+        <v>2296</v>
       </c>
       <c r="J24" s="14">
-        <v>2313</v>
+        <v>2583</v>
       </c>
       <c r="K24" s="15">
-        <v>-12.062256809338</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L24" s="15">
-        <v>-30.175077239958</v>
+        <v>-28.651336233685</v>
       </c>
       <c r="M24" s="15">
-        <v>54.676806083650</v>
+        <v>52.254641909814</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D25" s="14">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E25" s="15">
-        <v>-42.458100558659</v>
+        <v>-37.297297297297</v>
       </c>
       <c r="F25" s="14">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="G25" s="14">
-        <v>710</v>
+        <v>735</v>
       </c>
       <c r="H25" s="15">
-        <v>-32.253521126760</v>
+        <v>-32.244897959183</v>
       </c>
       <c r="I25" s="14">
-        <v>1048</v>
+        <v>1159</v>
       </c>
       <c r="J25" s="14">
-        <v>1440</v>
+        <v>1625</v>
       </c>
       <c r="K25" s="15">
-        <v>-27.222222222222</v>
+        <v>-28.676923076923</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.419787590832</v>
+        <v>-41.846462619167</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D26" s="14">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="E26" s="15">
-        <v>-20.202020202020</v>
+        <v>-32.456140350877</v>
       </c>
       <c r="F26" s="14">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="G26" s="14">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="H26" s="15">
-        <v>6.590257879656</v>
+        <v>-8.072916666666</v>
       </c>
       <c r="I26" s="14">
-        <v>779</v>
+        <v>851</v>
       </c>
       <c r="J26" s="14">
-        <v>784</v>
+        <v>898</v>
       </c>
       <c r="K26" s="15">
-        <v>-0.637755102040</v>
+        <v>-5.233853006681</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.076749435665</v>
+        <v>-13.866396761133</v>
       </c>
       <c r="M26" s="15">
-        <v>6.275579809004</v>
+        <v>2.653799758745</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E27" s="15">
-        <v>166.666666666667</v>
+        <v>40</v>
       </c>
       <c r="F27" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G27" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H27" s="15">
-        <v>38.095238095238</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I27" s="14">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J27" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K27" s="15">
-        <v>17.391304347826</v>
+        <v>19.607843137254</v>
       </c>
       <c r="L27" s="15">
-        <v>38.461538461538</v>
+        <v>38.636363636363</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D28" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E28" s="15">
-        <v>-8.333333333333</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F28" s="14">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G28" s="14">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H28" s="15">
-        <v>-14.285714285714</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="I28" s="14">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="J28" s="14">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="K28" s="15">
-        <v>-24.444444444444</v>
+        <v>-22.680412371134</v>
       </c>
       <c r="L28" s="15">
-        <v>-22.727272727272</v>
+        <v>-27.184466019417</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>-28.571428571428</v>
       </c>
       <c r="L29" s="15">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="M29" s="15">
         <v>-28.571428571428</v>
       </c>
       <c r="N29" s="15">
-        <v>-89.583333333333</v>
+        <v>-90.740740740740</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,48 +1535,48 @@
         <v>-28.571428571428</v>
       </c>
       <c r="L30" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M30" s="15">
         <v>-16.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-89.583333333333</v>
+        <v>-90.566037735849</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F31" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G31" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H31" s="15">
-        <v>33.333333333333</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I31" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J31" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K31" s="15">
-        <v>75</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>-6.25</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,20 +1610,20 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F33" s="14">
-        <v>2</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="14">
         <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>5</v>
@@ -1635,7 +1635,7 @@
         <v>66.666666666666</v>
       </c>
       <c r="L33" s="15">
-        <v>-54.545454545454</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbqn.xlsx
+++ b/data/source/weekly/cs-en-us-pbqn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -861,31 +861,31 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>1</v>
-      </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="14">
         <v>5</v>
       </c>
       <c r="K14" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M14" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="N14" s="15">
-        <v>-92.857142857142</v>
+        <v>-90.322580645161</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
+        <v>300</v>
+      </c>
+      <c r="F15" s="14">
         <v>25</v>
       </c>
-      <c r="F15" s="14">
-        <v>21</v>
-      </c>
       <c r="G15" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="15">
-        <v>61.538461538461</v>
+        <v>78.571428571428</v>
       </c>
       <c r="I15" s="14">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="J15" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K15" s="15">
-        <v>31.578947368421</v>
+        <v>45</v>
       </c>
       <c r="L15" s="15">
-        <v>72.413793103448</v>
+        <v>56.756756756756</v>
       </c>
       <c r="M15" s="15">
-        <v>138.095238095238</v>
+        <v>176.190476190476</v>
       </c>
       <c r="N15" s="15">
-        <v>51.515151515151</v>
+        <v>61.111111111111</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D16" s="14">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E16" s="15">
-        <v>-16.666666666666</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="F16" s="14">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G16" s="14">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H16" s="15">
-        <v>5.154639175257</v>
+        <v>-6.542056074766</v>
       </c>
       <c r="I16" s="14">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="J16" s="14">
-        <v>229</v>
+        <v>263</v>
       </c>
       <c r="K16" s="15">
-        <v>3.493449781659</v>
+        <v>-0.760456273764</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.386189258312</v>
+        <v>-40</v>
       </c>
       <c r="M16" s="15">
-        <v>-34.890109890109</v>
+        <v>-35.396039603960</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.647887323943</v>
+        <v>-86.363636363636</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D17" s="14">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E17" s="15">
-        <v>-24.528301886792</v>
+        <v>-36</v>
       </c>
       <c r="F17" s="14">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G17" s="14">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="H17" s="15">
-        <v>-13.478260869565</v>
+        <v>-23.046875</v>
       </c>
       <c r="I17" s="14">
-        <v>446</v>
+        <v>496</v>
       </c>
       <c r="J17" s="14">
-        <v>535</v>
+        <v>610</v>
       </c>
       <c r="K17" s="15">
-        <v>-16.635514018691</v>
+        <v>-18.688524590163</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.507936507936</v>
+        <v>-11.900532859680</v>
       </c>
       <c r="M17" s="15">
-        <v>92.241379310344</v>
+        <v>85.767790262172</v>
       </c>
       <c r="N17" s="15">
-        <v>-1.108647450110</v>
+        <v>1.639344262295</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D18" s="14">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E18" s="15">
-        <v>-36.842105263157</v>
+        <v>6.060606060606</v>
       </c>
       <c r="F18" s="14">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="G18" s="14">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="H18" s="15">
-        <v>-34.415584415584</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I18" s="14">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="J18" s="14">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="K18" s="15">
-        <v>-43.085106382978</v>
+        <v>-38.875305623471</v>
       </c>
       <c r="L18" s="15">
-        <v>-44.702842377261</v>
+        <v>-39.759036144578</v>
       </c>
       <c r="M18" s="15">
-        <v>-60.948905109489</v>
+        <v>-58.193979933110</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.718611772711</v>
+        <v>-92.204552541315</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D19" s="14">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="E19" s="15">
-        <v>-12.096774193548</v>
+        <v>4.123711340206</v>
       </c>
       <c r="F19" s="14">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="G19" s="14">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="H19" s="15">
-        <v>-2.163461538461</v>
+        <v>-1.225490196078</v>
       </c>
       <c r="I19" s="14">
-        <v>995</v>
+        <v>1095</v>
       </c>
       <c r="J19" s="14">
-        <v>939</v>
+        <v>1036</v>
       </c>
       <c r="K19" s="15">
-        <v>5.963791267305</v>
+        <v>5.694980694980</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.463629096722</v>
+        <v>-19.128508124076</v>
       </c>
       <c r="M19" s="15">
-        <v>45.894428152492</v>
+        <v>44.649933949801</v>
       </c>
       <c r="N19" s="15">
-        <v>-28.468727534148</v>
+        <v>-26.262626262626</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="D20" s="14">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E20" s="15">
-        <v>29.729729729729</v>
+        <v>106.060606060606</v>
       </c>
       <c r="F20" s="14">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="G20" s="14">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="H20" s="15">
-        <v>29.323308270676</v>
+        <v>38.356164383561</v>
       </c>
       <c r="I20" s="14">
-        <v>364</v>
+        <v>433</v>
       </c>
       <c r="J20" s="14">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="K20" s="15">
-        <v>15.923566878980</v>
+        <v>24.783861671469</v>
       </c>
       <c r="L20" s="15">
-        <v>-7.614213197969</v>
+        <v>-0.459770114942</v>
       </c>
       <c r="M20" s="15">
-        <v>24.232081911262</v>
+        <v>31.610942249240</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.809180918091</v>
+        <v>-90.960334029227</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="D21" s="17">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.785714285714</v>
+        <v>3.284671532846</v>
       </c>
       <c r="F21" s="17">
-        <v>1003</v>
+        <v>1049</v>
       </c>
       <c r="G21" s="17">
-        <v>1044</v>
+        <v>1071</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.927203065134</v>
+        <v>-2.054154995331</v>
       </c>
       <c r="I21" s="17">
-        <v>2308</v>
+        <v>2596</v>
       </c>
       <c r="J21" s="17">
-        <v>2436</v>
+        <v>2710</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.254515599343</v>
+        <v>-4.206642066420</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.974306964165</v>
+        <v>-19.901265041653</v>
       </c>
       <c r="M21" s="18">
-        <v>7.649253731343</v>
+        <v>9.029819403611</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.133893861314</v>
+        <v>-78.277968370847</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E22" s="15">
-        <v>-62.5</v>
+        <v>-60</v>
       </c>
       <c r="F22" s="14">
         <v>14</v>
       </c>
       <c r="G22" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H22" s="15">
-        <v>-46.153846153846</v>
+        <v>-44</v>
       </c>
       <c r="I22" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J22" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K22" s="15">
-        <v>-8</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>-9.803921568627</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>17.948717948717</v>
+        <v>21.951219512195</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>6</v>
+      </c>
+      <c r="D23" s="14">
         <v>4</v>
       </c>
-      <c r="D23" s="14">
-        <v>5</v>
-      </c>
       <c r="E23" s="15">
-        <v>-20</v>
+        <v>50</v>
       </c>
       <c r="F23" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G23" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H23" s="15">
-        <v>-14.285714285714</v>
+        <v>-5</v>
       </c>
       <c r="I23" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J23" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K23" s="15">
-        <v>-17.777777777777</v>
+        <v>-12.244897959183</v>
       </c>
       <c r="L23" s="15">
-        <v>-17.777777777777</v>
+        <v>-10.416666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>27.586206896551</v>
+        <v>38.709677419354</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>277</v>
+        <v>252</v>
       </c>
       <c r="D24" s="14">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="E24" s="15">
-        <v>2.592592592592</v>
+        <v>-10.638297872340</v>
       </c>
       <c r="F24" s="14">
-        <v>948</v>
+        <v>963</v>
       </c>
       <c r="G24" s="14">
         <v>1109</v>
       </c>
       <c r="H24" s="15">
-        <v>-14.517583408476</v>
+        <v>-13.165013525698</v>
       </c>
       <c r="I24" s="14">
-        <v>2296</v>
+        <v>2552</v>
       </c>
       <c r="J24" s="14">
-        <v>2583</v>
+        <v>2865</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.111111111111</v>
+        <v>-10.924956369982</v>
       </c>
       <c r="L24" s="15">
-        <v>-28.651336233685</v>
+        <v>-26.792885829030</v>
       </c>
       <c r="M24" s="15">
-        <v>52.254641909814</v>
+        <v>53.457606734816</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D25" s="14">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="E25" s="15">
-        <v>-37.297297297297</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="F25" s="14">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="G25" s="14">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="H25" s="15">
-        <v>-32.244897959183</v>
+        <v>-34.289617486338</v>
       </c>
       <c r="I25" s="14">
-        <v>1159</v>
+        <v>1282</v>
       </c>
       <c r="J25" s="14">
-        <v>1625</v>
+        <v>1800</v>
       </c>
       <c r="K25" s="15">
-        <v>-28.676923076923</v>
+        <v>-28.777777777777</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.846462619167</v>
+        <v>-40.565600370885</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="D26" s="14">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E26" s="15">
-        <v>-32.456140350877</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="G26" s="14">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.072916666666</v>
+        <v>-10.776942355889</v>
       </c>
       <c r="I26" s="14">
-        <v>851</v>
+        <v>954</v>
       </c>
       <c r="J26" s="14">
-        <v>898</v>
+        <v>1003</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.233853006681</v>
+        <v>-4.885343968095</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.866396761133</v>
+        <v>-13.821138211382</v>
       </c>
       <c r="M26" s="15">
-        <v>2.653799758745</v>
+        <v>3.135135135135</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E27" s="15">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="F27" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G27" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H27" s="15">
-        <v>44.444444444444</v>
+        <v>57.894736842105</v>
       </c>
       <c r="I27" s="14">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="J27" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K27" s="15">
-        <v>19.607843137254</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L27" s="15">
-        <v>38.636363636363</v>
+        <v>29.629629629629</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D28" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E28" s="15">
-        <v>-14.285714285714</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F28" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G28" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H28" s="15">
-        <v>-21.621621621621</v>
+        <v>-25.581395348837</v>
       </c>
       <c r="I28" s="14">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J28" s="14">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="K28" s="15">
-        <v>-22.680412371134</v>
+        <v>-24.545454545454</v>
       </c>
       <c r="L28" s="15">
-        <v>-27.184466019417</v>
+        <v>-27.826086956521</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
         <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I29" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K29" s="15">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="L29" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M29" s="15">
-        <v>-28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.740740740740</v>
+        <v>-89.090909090909</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="14">
         <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K30" s="15">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="L30" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="M30" s="15">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.566037735849</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1549,34 +1549,34 @@
         <v>38</v>
       </c>
       <c r="C31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="15">
         <v>0</v>
       </c>
       <c r="F31" s="14">
+        <v>5</v>
+      </c>
+      <c r="G31" s="14">
         <v>6</v>
       </c>
-      <c r="G31" s="14">
-        <v>7</v>
-      </c>
       <c r="H31" s="15">
-        <v>-14.285714285714</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I31" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J31" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K31" s="15">
-        <v>66.666666666666</v>
+        <v>54.545454545454</v>
       </c>
       <c r="L31" s="15">
-        <v>-6.25</v>
+        <v>6.25</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1629,13 +1629,13 @@
         <v>5</v>
       </c>
       <c r="J33" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L33" s="15">
-        <v>-58.333333333333</v>
+        <v>-68.75</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbqn.xlsx
+++ b/data/source/weekly/cs-en-us-pbqn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -879,13 +879,13 @@
         <v>-40</v>
       </c>
       <c r="L14" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-90.322580645161</v>
+        <v>-91.176470588235</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
         <v>8</v>
       </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
       <c r="E15" s="15">
-        <v>300</v>
+        <v>-87.5</v>
       </c>
       <c r="F15" s="14">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G15" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H15" s="15">
-        <v>78.571428571428</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I15" s="14">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J15" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K15" s="15">
-        <v>45</v>
+        <v>18.75</v>
       </c>
       <c r="L15" s="15">
-        <v>56.756756756756</v>
+        <v>35.714285714285</v>
       </c>
       <c r="M15" s="15">
-        <v>176.190476190476</v>
+        <v>137.5</v>
       </c>
       <c r="N15" s="15">
-        <v>61.111111111111</v>
+        <v>46.153846153846</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D16" s="14">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16" s="15">
-        <v>-35.294117647058</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="F16" s="14">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G16" s="14">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H16" s="15">
-        <v>-6.542056074766</v>
+        <v>-20.869565217391</v>
       </c>
       <c r="I16" s="14">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="J16" s="14">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="K16" s="15">
-        <v>-0.760456273764</v>
+        <v>-3.389830508474</v>
       </c>
       <c r="L16" s="15">
-        <v>-40</v>
+        <v>-39.618644067796</v>
       </c>
       <c r="M16" s="15">
-        <v>-35.396039603960</v>
+        <v>-34.180138568129</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.363636363636</v>
+        <v>-86.486486486486</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="D17" s="14">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E17" s="15">
-        <v>-36</v>
+        <v>11.290322580645</v>
       </c>
       <c r="F17" s="14">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="G17" s="14">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="H17" s="15">
-        <v>-23.046875</v>
+        <v>-18.250950570342</v>
       </c>
       <c r="I17" s="14">
-        <v>496</v>
+        <v>568</v>
       </c>
       <c r="J17" s="14">
-        <v>610</v>
+        <v>672</v>
       </c>
       <c r="K17" s="15">
-        <v>-18.688524590163</v>
+        <v>-15.476190476190</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.900532859680</v>
+        <v>-10.551181102362</v>
       </c>
       <c r="M17" s="15">
-        <v>85.767790262172</v>
+        <v>87.458745874587</v>
       </c>
       <c r="N17" s="15">
-        <v>1.639344262295</v>
+        <v>6.566604127579</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D18" s="14">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E18" s="15">
-        <v>6.060606060606</v>
+        <v>-42.5</v>
       </c>
       <c r="F18" s="14">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="G18" s="14">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="H18" s="15">
-        <v>-14.285714285714</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I18" s="14">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="J18" s="14">
-        <v>409</v>
+        <v>449</v>
       </c>
       <c r="K18" s="15">
-        <v>-38.875305623471</v>
+        <v>-38.752783964365</v>
       </c>
       <c r="L18" s="15">
-        <v>-39.759036144578</v>
+        <v>-39.293598233995</v>
       </c>
       <c r="M18" s="15">
-        <v>-58.193979933110</v>
+        <v>-58.143074581430</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.204552541315</v>
+        <v>-91.984844068784</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D19" s="14">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E19" s="15">
-        <v>4.123711340206</v>
+        <v>33.734939759036</v>
       </c>
       <c r="F19" s="14">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="G19" s="14">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="H19" s="15">
-        <v>-1.225490196078</v>
+        <v>2.227722772277</v>
       </c>
       <c r="I19" s="14">
-        <v>1095</v>
+        <v>1213</v>
       </c>
       <c r="J19" s="14">
-        <v>1036</v>
+        <v>1119</v>
       </c>
       <c r="K19" s="15">
-        <v>5.694980694980</v>
+        <v>8.400357462019</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.128508124076</v>
+        <v>-18.645204560697</v>
       </c>
       <c r="M19" s="15">
-        <v>44.649933949801</v>
+        <v>44.749403341288</v>
       </c>
       <c r="N19" s="15">
-        <v>-26.262626262626</v>
+        <v>-26.261398176291</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D20" s="14">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E20" s="15">
-        <v>106.060606060606</v>
+        <v>26.190476190476</v>
       </c>
       <c r="F20" s="14">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G20" s="14">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H20" s="15">
-        <v>38.356164383561</v>
+        <v>34.437086092715</v>
       </c>
       <c r="I20" s="14">
-        <v>433</v>
+        <v>487</v>
       </c>
       <c r="J20" s="14">
-        <v>347</v>
+        <v>389</v>
       </c>
       <c r="K20" s="15">
-        <v>24.783861671469</v>
+        <v>25.192802056555</v>
       </c>
       <c r="L20" s="15">
-        <v>-0.459770114942</v>
+        <v>-0.612244897959</v>
       </c>
       <c r="M20" s="15">
-        <v>31.610942249240</v>
+        <v>34.159779614325</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.960334029227</v>
+        <v>-90.609332819128</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D21" s="17">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E21" s="18">
-        <v>3.284671532846</v>
+        <v>5.223880597014</v>
       </c>
       <c r="F21" s="17">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="G21" s="17">
-        <v>1071</v>
+        <v>1104</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.054154995331</v>
+        <v>-4.438405797101</v>
       </c>
       <c r="I21" s="17">
-        <v>2596</v>
+        <v>2888</v>
       </c>
       <c r="J21" s="17">
-        <v>2710</v>
+        <v>2977</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.206642066420</v>
+        <v>-2.989586832381</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.901265041653</v>
+        <v>-19.464584495259</v>
       </c>
       <c r="M21" s="18">
-        <v>9.029819403611</v>
+        <v>10.060975609756</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.277968370847</v>
+        <v>-77.745241581259</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" s="14">
         <v>10</v>
       </c>
       <c r="E22" s="15">
-        <v>-60</v>
+        <v>-70</v>
       </c>
       <c r="F22" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G22" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H22" s="15">
-        <v>-44</v>
+        <v>-64.516129032258</v>
       </c>
       <c r="I22" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J22" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K22" s="15">
-        <v>-16.666666666666</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="L22" s="15">
-        <v>-16.666666666666</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="M22" s="15">
-        <v>21.951219512195</v>
+        <v>20.930232558139</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>22</v>
+      </c>
+      <c r="G23" s="14">
+        <v>16</v>
+      </c>
+      <c r="H23" s="15">
+        <v>37.5</v>
+      </c>
+      <c r="I23" s="14">
         <v>50</v>
       </c>
-      <c r="F23" s="14">
-        <v>19</v>
-      </c>
-      <c r="G23" s="14">
-        <v>20</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-5</v>
-      </c>
-      <c r="I23" s="14">
-        <v>43</v>
-      </c>
       <c r="J23" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K23" s="15">
-        <v>-12.244897959183</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L23" s="15">
-        <v>-10.416666666666</v>
+        <v>-1.960784313725</v>
       </c>
       <c r="M23" s="15">
-        <v>38.709677419354</v>
+        <v>51.515151515151</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="D24" s="14">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="E24" s="15">
-        <v>-10.638297872340</v>
+        <v>10.902255639097</v>
       </c>
       <c r="F24" s="14">
-        <v>963</v>
+        <v>1031</v>
       </c>
       <c r="G24" s="14">
-        <v>1109</v>
+        <v>1092</v>
       </c>
       <c r="H24" s="15">
-        <v>-13.165013525698</v>
+        <v>-5.586080586080</v>
       </c>
       <c r="I24" s="14">
-        <v>2552</v>
+        <v>2847</v>
       </c>
       <c r="J24" s="14">
-        <v>2865</v>
+        <v>3131</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.924956369982</v>
+        <v>-9.070584477802</v>
       </c>
       <c r="L24" s="15">
-        <v>-26.792885829030</v>
+        <v>-24.782034346103</v>
       </c>
       <c r="M24" s="15">
-        <v>53.457606734816</v>
+        <v>53.394396551724</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="D25" s="14">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="E25" s="15">
-        <v>-31.428571428571</v>
+        <v>1.298701298701</v>
       </c>
       <c r="F25" s="14">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="G25" s="14">
-        <v>732</v>
+        <v>693</v>
       </c>
       <c r="H25" s="15">
-        <v>-34.289617486338</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I25" s="14">
-        <v>1282</v>
+        <v>1438</v>
       </c>
       <c r="J25" s="14">
-        <v>1800</v>
+        <v>1954</v>
       </c>
       <c r="K25" s="15">
-        <v>-28.777777777777</v>
+        <v>-26.407369498464</v>
       </c>
       <c r="L25" s="15">
-        <v>-40.565600370885</v>
+        <v>-38.938428874734</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="D26" s="14">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E26" s="15">
         <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="G26" s="14">
-        <v>399</v>
+        <v>438</v>
       </c>
       <c r="H26" s="15">
-        <v>-10.776942355889</v>
+        <v>-12.557077625570</v>
       </c>
       <c r="I26" s="14">
-        <v>954</v>
+        <v>1073</v>
       </c>
       <c r="J26" s="14">
-        <v>1003</v>
+        <v>1123</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.885343968095</v>
+        <v>-4.452359750667</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.821138211382</v>
+        <v>-13.327948303715</v>
       </c>
       <c r="M26" s="15">
-        <v>3.135135135135</v>
+        <v>4.580896686159</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
         <v>9</v>
       </c>
-      <c r="D27" s="14">
-        <v>4</v>
-      </c>
       <c r="E27" s="15">
-        <v>125</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="F27" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G27" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H27" s="15">
-        <v>57.894736842105</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I27" s="14">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J27" s="14">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="K27" s="15">
-        <v>27.272727272727</v>
+        <v>7.8125</v>
       </c>
       <c r="L27" s="15">
-        <v>29.629629629629</v>
+        <v>11.290322580645</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D28" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E28" s="15">
-        <v>-38.461538461538</v>
+        <v>40</v>
       </c>
       <c r="F28" s="14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G28" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H28" s="15">
-        <v>-25.581395348837</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I28" s="14">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="J28" s="14">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="K28" s="15">
-        <v>-24.545454545454</v>
+        <v>-19.166666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-27.826086956521</v>
+        <v>-22.4</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,31 +1476,31 @@
         <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J29" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K29" s="15">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L29" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M29" s="15">
-        <v>-33.333333333333</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N29" s="15">
-        <v>-89.090909090909</v>
+        <v>-88.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,31 +1517,31 @@
         <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K30" s="15">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L30" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.888888888888</v>
+        <v>-87.931034482758</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,32 +1551,32 @@
       <c r="C31" s="14">
         <v>2</v>
       </c>
-      <c r="D31" s="14">
-        <v>2</v>
-      </c>
-      <c r="E31" s="15">
-        <v>0</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G31" s="14">
         <v>6</v>
       </c>
       <c r="H31" s="15">
-        <v>-16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I31" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J31" s="14">
         <v>11</v>
       </c>
       <c r="K31" s="15">
-        <v>54.545454545454</v>
+        <v>90.909090909090</v>
       </c>
       <c r="L31" s="15">
-        <v>6.25</v>
+        <v>23.529411764705</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1620,7 +1620,7 @@
         <v>20</v>
       </c>
       <c r="G33" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" s="15">
         <v>-100</v>
@@ -1629,10 +1629,10 @@
         <v>5</v>
       </c>
       <c r="J33" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K33" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L33" s="15">
         <v>-68.75</v>

--- a/data/source/weekly/cs-en-us-pbqn.xlsx
+++ b/data/source/weekly/cs-en-us-pbqn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,366 +854,366 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+        <v>6</v>
+      </c>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>500</v>
       </c>
       <c r="I14" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J14" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K14" s="15">
-        <v>-40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M14" s="15">
-        <v>-50</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N14" s="15">
-        <v>-91.176470588235</v>
+        <v>-81.578947368421</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D15" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E15" s="15">
-        <v>-87.5</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>19</v>
       </c>
       <c r="G15" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H15" s="15">
-        <v>11.764705882352</v>
+        <v>-5</v>
       </c>
       <c r="I15" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J15" s="14">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K15" s="15">
-        <v>18.75</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>35.714285714285</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>137.5</v>
+        <v>103.225806451613</v>
       </c>
       <c r="N15" s="15">
-        <v>46.153846153846</v>
+        <v>53.658536585365</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D16" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E16" s="15">
-        <v>-24.242424242424</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="F16" s="14">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G16" s="14">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="H16" s="15">
-        <v>-20.869565217391</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I16" s="14">
-        <v>285</v>
+        <v>317</v>
       </c>
       <c r="J16" s="14">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="K16" s="15">
-        <v>-3.389830508474</v>
+        <v>-4.229607250755</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.618644067796</v>
+        <v>-38.446601941747</v>
       </c>
       <c r="M16" s="15">
-        <v>-34.180138568129</v>
+        <v>-30.936819172113</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.486486486486</v>
+        <v>-86.022927689594</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="D17" s="14">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E17" s="15">
-        <v>11.290322580645</v>
+        <v>29.268292682926</v>
       </c>
       <c r="F17" s="14">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G17" s="14">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="H17" s="15">
-        <v>-18.250950570342</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I17" s="14">
-        <v>568</v>
+        <v>624</v>
       </c>
       <c r="J17" s="14">
-        <v>672</v>
+        <v>713</v>
       </c>
       <c r="K17" s="15">
-        <v>-15.476190476190</v>
+        <v>-12.482468443197</v>
       </c>
       <c r="L17" s="15">
-        <v>-10.551181102362</v>
+        <v>-7.828655834564</v>
       </c>
       <c r="M17" s="15">
-        <v>87.458745874587</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N17" s="15">
-        <v>6.566604127579</v>
+        <v>6.849315068493</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D18" s="14">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" s="15">
-        <v>-42.5</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F18" s="14">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G18" s="14">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H18" s="15">
-        <v>-27.272727272727</v>
+        <v>-30</v>
       </c>
       <c r="I18" s="14">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="J18" s="14">
-        <v>449</v>
+        <v>488</v>
       </c>
       <c r="K18" s="15">
-        <v>-38.752783964365</v>
+        <v>-39.139344262295</v>
       </c>
       <c r="L18" s="15">
-        <v>-39.293598233995</v>
+        <v>-40</v>
       </c>
       <c r="M18" s="15">
-        <v>-58.143074581430</v>
+        <v>-57.388809182209</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.984844068784</v>
+        <v>-91.957757920389</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="D19" s="14">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="E19" s="15">
-        <v>33.734939759036</v>
+        <v>-22.413793103448</v>
       </c>
       <c r="F19" s="14">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="G19" s="14">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="H19" s="15">
-        <v>2.227722772277</v>
+        <v>-3.095238095238</v>
       </c>
       <c r="I19" s="14">
-        <v>1213</v>
+        <v>1299</v>
       </c>
       <c r="J19" s="14">
-        <v>1119</v>
+        <v>1235</v>
       </c>
       <c r="K19" s="15">
-        <v>8.400357462019</v>
+        <v>5.182186234817</v>
       </c>
       <c r="L19" s="15">
-        <v>-18.645204560697</v>
+        <v>-19.814814814814</v>
       </c>
       <c r="M19" s="15">
-        <v>44.749403341288</v>
+        <v>42.278203723986</v>
       </c>
       <c r="N19" s="15">
-        <v>-26.261398176291</v>
+        <v>-27.267637178051</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D20" s="14">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E20" s="15">
-        <v>26.190476190476</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="G20" s="14">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H20" s="15">
-        <v>34.437086092715</v>
+        <v>37.254901960784</v>
       </c>
       <c r="I20" s="14">
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="J20" s="14">
-        <v>389</v>
+        <v>430</v>
       </c>
       <c r="K20" s="15">
-        <v>25.192802056555</v>
+        <v>22.790697674418</v>
       </c>
       <c r="L20" s="15">
-        <v>-0.612244897959</v>
+        <v>0.380228136882</v>
       </c>
       <c r="M20" s="15">
-        <v>34.159779614325</v>
+        <v>32.663316582914</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.609332819128</v>
+        <v>-90.661478599221</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="D21" s="17">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="E21" s="18">
-        <v>5.223880597014</v>
+        <v>-13.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="G21" s="17">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.438405797101</v>
+        <v>-4.087193460490</v>
       </c>
       <c r="I21" s="17">
-        <v>2888</v>
+        <v>3135</v>
       </c>
       <c r="J21" s="17">
-        <v>2977</v>
+        <v>3257</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.989586832381</v>
+        <v>-3.745778323610</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.464584495259</v>
+        <v>-19.159360495100</v>
       </c>
       <c r="M21" s="18">
-        <v>10.060975609756</v>
+        <v>10.270840661273</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.745241581259</v>
+        <v>-77.709044368600</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>6</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-83.333333333333</v>
+      </c>
+      <c r="F22" s="14">
+        <v>10</v>
+      </c>
+      <c r="G22" s="14">
+        <v>34</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-70.588235294117</v>
+      </c>
+      <c r="I22" s="14">
+        <v>53</v>
+      </c>
+      <c r="J22" s="14">
+        <v>76</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-30.263157894736</v>
+      </c>
+      <c r="L22" s="15">
+        <v>-22.058823529411</v>
+      </c>
+      <c r="M22" s="15">
+        <v>10.416666666666</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="C22" s="14">
-        <v>3</v>
-      </c>
-      <c r="D22" s="14">
-        <v>10</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-70</v>
-      </c>
-      <c r="F22" s="14">
-        <v>11</v>
-      </c>
-      <c r="G22" s="14">
-        <v>31</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-64.516129032258</v>
-      </c>
-      <c r="I22" s="14">
-        <v>52</v>
-      </c>
-      <c r="J22" s="14">
-        <v>70</v>
-      </c>
-      <c r="K22" s="15">
-        <v>-25.714285714285</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-21.212121212121</v>
-      </c>
-      <c r="M22" s="15">
-        <v>20.930232558139</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1224,37 +1224,37 @@
         <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
         <v>22</v>
       </c>
       <c r="G23" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H23" s="15">
-        <v>37.5</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I23" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J23" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K23" s="15">
-        <v>-9.090909090909</v>
+        <v>-5.172413793103</v>
       </c>
       <c r="L23" s="15">
-        <v>-1.960784313725</v>
+        <v>-5.172413793103</v>
       </c>
       <c r="M23" s="15">
-        <v>51.515151515151</v>
+        <v>41.025641025641</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>295</v>
+        <v>258</v>
       </c>
       <c r="D24" s="14">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="E24" s="15">
-        <v>10.902255639097</v>
+        <v>-7.194244604316</v>
       </c>
       <c r="F24" s="14">
-        <v>1031</v>
+        <v>1090</v>
       </c>
       <c r="G24" s="14">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.586080586080</v>
+        <v>-0.547445255474</v>
       </c>
       <c r="I24" s="14">
-        <v>2847</v>
+        <v>3105</v>
       </c>
       <c r="J24" s="14">
-        <v>3131</v>
+        <v>3409</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.070584477802</v>
+        <v>-8.917571135230</v>
       </c>
       <c r="L24" s="15">
-        <v>-24.782034346103</v>
+        <v>-24.360535931790</v>
       </c>
       <c r="M24" s="15">
-        <v>53.394396551724</v>
+        <v>51.982378854625</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="D25" s="14">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="E25" s="15">
-        <v>1.298701298701</v>
+        <v>-31.284916201117</v>
       </c>
       <c r="F25" s="14">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="G25" s="14">
         <v>693</v>
       </c>
       <c r="H25" s="15">
-        <v>-28.571428571428</v>
+        <v>-24.819624819624</v>
       </c>
       <c r="I25" s="14">
-        <v>1438</v>
+        <v>1562</v>
       </c>
       <c r="J25" s="14">
-        <v>1954</v>
+        <v>2133</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.407369498464</v>
+        <v>-26.769807782466</v>
       </c>
       <c r="L25" s="15">
-        <v>-38.938428874734</v>
+        <v>-39.410395655546</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D26" s="14">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>8.247422680412</v>
       </c>
       <c r="F26" s="14">
-        <v>383</v>
+        <v>411</v>
       </c>
       <c r="G26" s="14">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H26" s="15">
-        <v>-12.557077625570</v>
+        <v>-5.733944954128</v>
       </c>
       <c r="I26" s="14">
-        <v>1073</v>
+        <v>1176</v>
       </c>
       <c r="J26" s="14">
-        <v>1123</v>
+        <v>1220</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.452359750667</v>
+        <v>-3.606557377049</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.327948303715</v>
+        <v>-12.759643916913</v>
       </c>
       <c r="M26" s="15">
-        <v>4.580896686159</v>
+        <v>4.906333630686</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D27" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E27" s="15">
-        <v>-88.888888888888</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G27" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H27" s="15">
-        <v>14.285714285714</v>
+        <v>-8</v>
       </c>
       <c r="I27" s="14">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="J27" s="14">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="K27" s="15">
-        <v>7.8125</v>
+        <v>7.042253521126</v>
       </c>
       <c r="L27" s="15">
-        <v>11.290322580645</v>
+        <v>18.75</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,54 +1426,54 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D28" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E28" s="15">
-        <v>40</v>
+        <v>157.142857142857</v>
       </c>
       <c r="F28" s="14">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G28" s="14">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H28" s="15">
-        <v>-7.142857142857</v>
+        <v>24.324324324324</v>
       </c>
       <c r="I28" s="14">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="J28" s="14">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="K28" s="15">
-        <v>-19.166666666666</v>
+        <v>-9.448818897637</v>
       </c>
       <c r="L28" s="15">
-        <v>-22.4</v>
+        <v>-14.179104477611</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
@@ -1497,24 +1497,24 @@
         <v>75</v>
       </c>
       <c r="M29" s="15">
-        <v>-22.222222222222</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.333333333333</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
@@ -1538,10 +1538,10 @@
         <v>133.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.931034482758</v>
+        <v>-88.524590163934</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1549,40 +1549,40 @@
         <v>38</v>
       </c>
       <c r="C31" s="14">
-        <v>2</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D31" s="14">
+        <v>4</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-75</v>
       </c>
       <c r="F31" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G31" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H31" s="15">
-        <v>33.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I31" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J31" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K31" s="15">
-        <v>90.909090909090</v>
+        <v>60</v>
       </c>
       <c r="L31" s="15">
-        <v>23.529411764705</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,41 +1607,41 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="14">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
+      <c r="E33" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" s="14">
         <v>1</v>
       </c>
-      <c r="E33" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="G33" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I33" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" s="14">
         <v>5</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L33" s="15">
-        <v>-68.75</v>
+        <v>-62.5</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>218</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>10079</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>2992</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>17454</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>11614</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>28509</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>71017</v>

--- a/data/source/weekly/cs-en-us-pbqn.xlsx
+++ b/data/source/weekly/cs-en-us-pbqn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -199,55 +199,55 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Petit Larceny</t>
+  </si>
+  <si>
+    <t>Retail Theft</t>
+  </si>
+  <si>
+    <t>Misd. Assault</t>
+  </si>
+  <si>
+    <t>UCR Rape*</t>
+  </si>
+  <si>
+    <t>Other Sex Crimes</t>
+  </si>
+  <si>
+    <t>Shooting Vic.</t>
+  </si>
+  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Petit Larceny</t>
-  </si>
-  <si>
-    <t>Retail Theft</t>
-  </si>
-  <si>
-    <t>Misd. Assault</t>
-  </si>
-  <si>
-    <t>UCR Rape*</t>
-  </si>
-  <si>
-    <t>Other Sex Crimes</t>
-  </si>
-  <si>
-    <t>Shooting Vic.</t>
   </si>
   <si>
     <t>Shooting Inc.</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -851,697 +851,697 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="14">
         <v>1</v>
       </c>
       <c r="E14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F14" s="14">
         <v>6</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="I14" s="14">
+        <v>8</v>
+      </c>
+      <c r="J14" s="14">
         <v>7</v>
       </c>
-      <c r="J14" s="14">
-        <v>6</v>
-      </c>
       <c r="K14" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L14" s="15">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="M14" s="15">
-        <v>-22.222222222222</v>
+        <v>-20</v>
       </c>
       <c r="N14" s="15">
-        <v>-81.578947368421</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
         <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G15" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H15" s="15">
-        <v>-5</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I15" s="14">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J15" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K15" s="15">
-        <v>16.666666666666</v>
+        <v>16.071428571428</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>51.162790697674</v>
       </c>
       <c r="M15" s="15">
-        <v>103.225806451613</v>
+        <v>103.125</v>
       </c>
       <c r="N15" s="15">
-        <v>53.658536585365</v>
+        <v>54.761904761904</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="14">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D16" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E16" s="15">
-        <v>-13.888888888888</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="F16" s="14">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="G16" s="14">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="H16" s="15">
-        <v>-21.428571428571</v>
+        <v>-24.113475177305</v>
       </c>
       <c r="I16" s="14">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="J16" s="14">
-        <v>331</v>
+        <v>370</v>
       </c>
       <c r="K16" s="15">
-        <v>-4.229607250755</v>
+        <v>-6.486486486486</v>
       </c>
       <c r="L16" s="15">
-        <v>-38.446601941747</v>
+        <v>-36.745886654479</v>
       </c>
       <c r="M16" s="15">
-        <v>-30.936819172113</v>
+        <v>-30.101010101010</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.022927689594</v>
+        <v>-85.767174002468</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="14">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D17" s="14">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E17" s="15">
-        <v>29.268292682926</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F17" s="14">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="G17" s="14">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="H17" s="15">
-        <v>-9.090909090909</v>
+        <v>-4.979253112033</v>
       </c>
       <c r="I17" s="14">
-        <v>624</v>
+        <v>684</v>
       </c>
       <c r="J17" s="14">
-        <v>713</v>
+        <v>776</v>
       </c>
       <c r="K17" s="15">
-        <v>-12.482468443197</v>
+        <v>-11.855670103092</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.828655834564</v>
+        <v>-8.064516129032</v>
       </c>
       <c r="M17" s="15">
-        <v>85.714285714285</v>
+        <v>89.473684210526</v>
       </c>
       <c r="N17" s="15">
-        <v>6.849315068493</v>
+        <v>8.571428571428</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="14">
         <v>21</v>
       </c>
       <c r="D18" s="14">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E18" s="15">
-        <v>-46.153846153846</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F18" s="14">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G18" s="14">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H18" s="15">
-        <v>-30</v>
+        <v>-29.655172413793</v>
       </c>
       <c r="I18" s="14">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="J18" s="14">
-        <v>488</v>
+        <v>521</v>
       </c>
       <c r="K18" s="15">
-        <v>-39.139344262295</v>
+        <v>-38.771593090211</v>
       </c>
       <c r="L18" s="15">
-        <v>-40</v>
+        <v>-39.353612167300</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.388809182209</v>
+        <v>-57.238605898123</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.957757920389</v>
+        <v>-91.926094659579</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="14">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="D19" s="14">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E19" s="15">
-        <v>-22.413793103448</v>
+        <v>-2.654867256637</v>
       </c>
       <c r="F19" s="14">
         <v>407</v>
       </c>
       <c r="G19" s="14">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="H19" s="15">
-        <v>-3.095238095238</v>
+        <v>-0.488997555012</v>
       </c>
       <c r="I19" s="14">
-        <v>1299</v>
+        <v>1408</v>
       </c>
       <c r="J19" s="14">
-        <v>1235</v>
+        <v>1348</v>
       </c>
       <c r="K19" s="15">
-        <v>5.182186234817</v>
+        <v>4.451038575667</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.814814814814</v>
+        <v>-18.234610917537</v>
       </c>
       <c r="M19" s="15">
-        <v>42.278203723986</v>
+        <v>42.799188640973</v>
       </c>
       <c r="N19" s="15">
-        <v>-27.267637178051</v>
+        <v>-27.310273618998</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="14">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D20" s="14">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="F20" s="14">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G20" s="14">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H20" s="15">
-        <v>37.254901960784</v>
+        <v>37.820512820512</v>
       </c>
       <c r="I20" s="14">
-        <v>528</v>
+        <v>581</v>
       </c>
       <c r="J20" s="14">
-        <v>430</v>
+        <v>470</v>
       </c>
       <c r="K20" s="15">
-        <v>22.790697674418</v>
+        <v>23.617021276595</v>
       </c>
       <c r="L20" s="15">
-        <v>0.380228136882</v>
+        <v>-1.190476190476</v>
       </c>
       <c r="M20" s="15">
-        <v>32.663316582914</v>
+        <v>32.951945080091</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.661478599221</v>
+        <v>-90.450361604207</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" s="17">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="D21" s="17">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.571428571428</v>
+        <v>-7.903780068728</v>
       </c>
       <c r="F21" s="17">
-        <v>1056</v>
+        <v>1082</v>
       </c>
       <c r="G21" s="17">
-        <v>1101</v>
+        <v>1112</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.087193460490</v>
+        <v>-2.697841726618</v>
       </c>
       <c r="I21" s="17">
-        <v>3135</v>
+        <v>3411</v>
       </c>
       <c r="J21" s="17">
-        <v>3257</v>
+        <v>3548</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.745778323610</v>
+        <v>-3.861330326944</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.159360495100</v>
+        <v>-18.279827503593</v>
       </c>
       <c r="M21" s="18">
-        <v>10.270840661273</v>
+        <v>11.216172155200</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.709044368600</v>
+        <v>-77.433013562686</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="14">
+        <v>4</v>
+      </c>
+      <c r="D22" s="14">
+        <v>9</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-55.555555555555</v>
+      </c>
+      <c r="F22" s="14">
+        <v>11</v>
+      </c>
+      <c r="G22" s="14">
+        <v>35</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-68.571428571428</v>
+      </c>
+      <c r="I22" s="14">
+        <v>57</v>
+      </c>
+      <c r="J22" s="14">
+        <v>85</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-32.941176470588</v>
+      </c>
+      <c r="L22" s="15">
+        <v>-21.917808219178</v>
+      </c>
+      <c r="M22" s="15">
+        <v>11.764705882352</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="14">
-        <v>6</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-83.333333333333</v>
-      </c>
-      <c r="F22" s="14">
-        <v>10</v>
-      </c>
-      <c r="G22" s="14">
-        <v>34</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-70.588235294117</v>
-      </c>
-      <c r="I22" s="14">
-        <v>53</v>
-      </c>
-      <c r="J22" s="14">
-        <v>76</v>
-      </c>
-      <c r="K22" s="15">
-        <v>-30.263157894736</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-22.058823529411</v>
-      </c>
-      <c r="M22" s="15">
-        <v>10.416666666666</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
         <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G23" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H23" s="15">
-        <v>22.222222222222</v>
+        <v>25</v>
       </c>
       <c r="I23" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J23" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K23" s="15">
-        <v>-5.172413793103</v>
+        <v>-4.918032786885</v>
       </c>
       <c r="L23" s="15">
-        <v>-5.172413793103</v>
+        <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>41.025641025641</v>
+        <v>41.463414634146</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="14">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="D24" s="14">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E24" s="15">
-        <v>-7.194244604316</v>
+        <v>-25.992779783393</v>
       </c>
       <c r="F24" s="14">
-        <v>1090</v>
+        <v>1013</v>
       </c>
       <c r="G24" s="14">
-        <v>1096</v>
+        <v>1103</v>
       </c>
       <c r="H24" s="15">
-        <v>-0.547445255474</v>
+        <v>-8.159564823209</v>
       </c>
       <c r="I24" s="14">
-        <v>3105</v>
+        <v>3309</v>
       </c>
       <c r="J24" s="14">
-        <v>3409</v>
+        <v>3686</v>
       </c>
       <c r="K24" s="15">
-        <v>-8.917571135230</v>
+        <v>-10.227889310906</v>
       </c>
       <c r="L24" s="15">
-        <v>-24.360535931790</v>
+        <v>-24.863760217983</v>
       </c>
       <c r="M24" s="15">
-        <v>51.982378854625</v>
+        <v>51.510989010989</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="14">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="D25" s="14">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="E25" s="15">
-        <v>-31.284916201117</v>
+        <v>-50.602409638554</v>
       </c>
       <c r="F25" s="14">
-        <v>521</v>
+        <v>483</v>
       </c>
       <c r="G25" s="14">
-        <v>693</v>
+        <v>674</v>
       </c>
       <c r="H25" s="15">
-        <v>-24.819624819624</v>
+        <v>-28.338278931750</v>
       </c>
       <c r="I25" s="14">
-        <v>1562</v>
+        <v>1644</v>
       </c>
       <c r="J25" s="14">
-        <v>2133</v>
+        <v>2299</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.769807782466</v>
+        <v>-28.490648107873</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.410395655546</v>
+        <v>-40.477914554670</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="14">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D26" s="14">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E26" s="15">
-        <v>8.247422680412</v>
+        <v>5.607476635514</v>
       </c>
       <c r="F26" s="14">
-        <v>411</v>
+        <v>444</v>
       </c>
       <c r="G26" s="14">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="H26" s="15">
-        <v>-5.733944954128</v>
+        <v>3.496503496503</v>
       </c>
       <c r="I26" s="14">
-        <v>1176</v>
+        <v>1285</v>
       </c>
       <c r="J26" s="14">
-        <v>1220</v>
+        <v>1327</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.606557377049</v>
+        <v>-3.165033911077</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.759643916913</v>
+        <v>-12.046543463381</v>
       </c>
       <c r="M26" s="15">
-        <v>4.906333630686</v>
+        <v>7.262103505843</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="F27" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G27" s="14">
         <v>25</v>
       </c>
       <c r="H27" s="15">
-        <v>-8</v>
+        <v>-28</v>
       </c>
       <c r="I27" s="14">
+        <v>78</v>
+      </c>
+      <c r="J27" s="14">
         <v>76</v>
       </c>
-      <c r="J27" s="14">
-        <v>71</v>
-      </c>
       <c r="K27" s="15">
-        <v>7.042253521126</v>
+        <v>2.631578947368</v>
       </c>
       <c r="L27" s="15">
-        <v>18.75</v>
+        <v>14.705882352941</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D28" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E28" s="15">
-        <v>157.142857142857</v>
+        <v>58.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G28" s="14">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H28" s="15">
-        <v>24.324324324324</v>
+        <v>40.476190476190</v>
       </c>
       <c r="I28" s="14">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="J28" s="14">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="K28" s="15">
-        <v>-9.448818897637</v>
+        <v>-3.597122302158</v>
       </c>
       <c r="L28" s="15">
-        <v>-14.179104477611</v>
+        <v>-6.944444444444</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="E29" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I29" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J29" s="14">
         <v>9</v>
       </c>
       <c r="K29" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L29" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M29" s="15">
-        <v>-46.153846153846</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.888888888888</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
         <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I30" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J30" s="14">
         <v>9</v>
       </c>
       <c r="K30" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L30" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M30" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.524590163934</v>
+        <v>-87.878787878787</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1549,40 +1549,40 @@
         <v>38</v>
       </c>
       <c r="C31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F31" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G31" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H31" s="15">
-        <v>57.142857142857</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I31" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J31" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K31" s="15">
-        <v>60</v>
+        <v>44.444444444444</v>
       </c>
       <c r="L31" s="15">
-        <v>14.285714285714</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,40 +1608,40 @@
         <v>40</v>
       </c>
       <c r="C33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F33" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33" s="14">
         <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="I33" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J33" s="14">
         <v>5</v>
       </c>
       <c r="K33" s="15">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="L33" s="15">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>218</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14">
         <v>10079</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="14">
         <v>2992</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C43" s="14">
         <v>17454</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14">
         <v>11614</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C45" s="14">
         <v>28509</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C46" s="17">
         <v>71017</v>

--- a/data/source/weekly/cs-en-us-pbqn.xlsx
+++ b/data/source/weekly/cs-en-us-pbqn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -199,6 +199,9 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -245,9 +248,6 @@
   </si>
   <si>
     <t>Shooting Vic.</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>Shooting Inc.</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -851,32 +851,32 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="14">
         <v>1</v>
       </c>
       <c r="E14" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="15">
-        <v>200</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I14" s="14">
         <v>8</v>
       </c>
       <c r="J14" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K14" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L14" s="15">
         <v>100</v>
@@ -890,13 +890,13 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E15" s="15">
         <v>0</v>
@@ -905,602 +905,602 @@
         <v>16</v>
       </c>
       <c r="G15" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H15" s="15">
-        <v>-11.111111111111</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="I15" s="14">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="J15" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K15" s="15">
-        <v>16.071428571428</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L15" s="15">
-        <v>51.162790697674</v>
+        <v>46.938775510204</v>
       </c>
       <c r="M15" s="15">
-        <v>103.125</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>54.761904761904</v>
+        <v>63.636363636363</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D16" s="14">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E16" s="15">
-        <v>-25.641025641025</v>
+        <v>26.923076923076</v>
       </c>
       <c r="F16" s="14">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="G16" s="14">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H16" s="15">
-        <v>-24.113475177305</v>
+        <v>-11.940298507462</v>
       </c>
       <c r="I16" s="14">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="J16" s="14">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="K16" s="15">
-        <v>-6.486486486486</v>
+        <v>-4.292929292929</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.745886654479</v>
+        <v>-34.879725085910</v>
       </c>
       <c r="M16" s="15">
-        <v>-30.101010101010</v>
+        <v>-27.671755725190</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.767174002468</v>
+        <v>-85.258654220147</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D17" s="14">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E17" s="15">
-        <v>-14.285714285714</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G17" s="14">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="H17" s="15">
-        <v>-4.979253112033</v>
+        <v>5.607476635514</v>
       </c>
       <c r="I17" s="14">
-        <v>684</v>
+        <v>735</v>
       </c>
       <c r="J17" s="14">
-        <v>776</v>
+        <v>824</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.855670103092</v>
+        <v>-10.800970873786</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.064516129032</v>
+        <v>-8.239700374531</v>
       </c>
       <c r="M17" s="15">
-        <v>89.473684210526</v>
+        <v>85.138539042821</v>
       </c>
       <c r="N17" s="15">
-        <v>8.571428571428</v>
+        <v>5.150214592274</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D18" s="14">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E18" s="15">
-        <v>-36.363636363636</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="F18" s="14">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="G18" s="14">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="H18" s="15">
-        <v>-29.655172413793</v>
+        <v>-46.103896103896</v>
       </c>
       <c r="I18" s="14">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="J18" s="14">
-        <v>521</v>
+        <v>563</v>
       </c>
       <c r="K18" s="15">
-        <v>-38.771593090211</v>
+        <v>-40.319715808170</v>
       </c>
       <c r="L18" s="15">
-        <v>-39.353612167300</v>
+        <v>-39.350180505415</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.238605898123</v>
+        <v>-57.629255989911</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.926094659579</v>
+        <v>-92.041686404547</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="D19" s="14">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E19" s="15">
-        <v>-2.654867256637</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="F19" s="14">
-        <v>407</v>
+        <v>378</v>
       </c>
       <c r="G19" s="14">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="H19" s="15">
-        <v>-0.488997555012</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="I19" s="14">
-        <v>1408</v>
+        <v>1488</v>
       </c>
       <c r="J19" s="14">
-        <v>1348</v>
+        <v>1450</v>
       </c>
       <c r="K19" s="15">
-        <v>4.451038575667</v>
+        <v>2.620689655172</v>
       </c>
       <c r="L19" s="15">
-        <v>-18.234610917537</v>
+        <v>-19.174361759913</v>
       </c>
       <c r="M19" s="15">
-        <v>42.799188640973</v>
+        <v>38.805970149253</v>
       </c>
       <c r="N19" s="15">
-        <v>-27.310273618998</v>
+        <v>-28.219971056439</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D20" s="14">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E20" s="15">
-        <v>27.5</v>
+        <v>19.230769230769</v>
       </c>
       <c r="F20" s="14">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="G20" s="14">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="H20" s="15">
-        <v>37.820512820512</v>
+        <v>18.285714285714</v>
       </c>
       <c r="I20" s="14">
-        <v>581</v>
+        <v>643</v>
       </c>
       <c r="J20" s="14">
-        <v>470</v>
+        <v>522</v>
       </c>
       <c r="K20" s="15">
-        <v>23.617021276595</v>
+        <v>23.180076628352</v>
       </c>
       <c r="L20" s="15">
-        <v>-1.190476190476</v>
+        <v>0.783699059561</v>
       </c>
       <c r="M20" s="15">
-        <v>32.951945080091</v>
+        <v>35.084033613445</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.450361604207</v>
+        <v>-90.163683646932</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="D21" s="17">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.903780068728</v>
+        <v>-12.230215827338</v>
       </c>
       <c r="F21" s="17">
-        <v>1082</v>
+        <v>1033</v>
       </c>
       <c r="G21" s="17">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.697841726618</v>
+        <v>-7.520143240823</v>
       </c>
       <c r="I21" s="17">
-        <v>3411</v>
+        <v>3661</v>
       </c>
       <c r="J21" s="17">
-        <v>3548</v>
+        <v>3826</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.861330326944</v>
+        <v>-4.312598013591</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.279827503593</v>
+        <v>-18.080107406578</v>
       </c>
       <c r="M21" s="18">
-        <v>11.216172155200</v>
+        <v>10.671100362757</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.433013562686</v>
+        <v>-77.381687878413</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" s="15">
-        <v>-55.555555555555</v>
+        <v>-87.5</v>
       </c>
       <c r="F22" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G22" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H22" s="15">
-        <v>-68.571428571428</v>
+        <v>-75.757575757575</v>
       </c>
       <c r="I22" s="14">
         <v>57</v>
       </c>
       <c r="J22" s="14">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K22" s="15">
-        <v>-32.941176470588</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="L22" s="15">
-        <v>-21.917808219178</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="M22" s="15">
-        <v>11.764705882352</v>
+        <v>3.636363636363</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
         <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G23" s="14">
         <v>16</v>
       </c>
       <c r="H23" s="15">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="I23" s="14">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J23" s="14">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K23" s="15">
-        <v>-4.918032786885</v>
+        <v>-4.615384615384</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>3.333333333333</v>
       </c>
       <c r="M23" s="15">
-        <v>41.463414634146</v>
+        <v>47.619047619047</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="D24" s="14">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E24" s="15">
-        <v>-25.992779783393</v>
+        <v>-18.996415770609</v>
       </c>
       <c r="F24" s="14">
-        <v>1013</v>
+        <v>985</v>
       </c>
       <c r="G24" s="14">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.159564823209</v>
+        <v>-10.454545454545</v>
       </c>
       <c r="I24" s="14">
-        <v>3309</v>
+        <v>3536</v>
       </c>
       <c r="J24" s="14">
-        <v>3686</v>
+        <v>3965</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.227889310906</v>
+        <v>-10.819672131147</v>
       </c>
       <c r="L24" s="15">
-        <v>-24.863760217983</v>
+        <v>-24.136451405277</v>
       </c>
       <c r="M24" s="15">
-        <v>51.510989010989</v>
+        <v>47.517730496453</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="D25" s="14">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="E25" s="15">
-        <v>-50.602409638554</v>
+        <v>-33.116883116883</v>
       </c>
       <c r="F25" s="14">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="G25" s="14">
-        <v>674</v>
+        <v>653</v>
       </c>
       <c r="H25" s="15">
-        <v>-28.338278931750</v>
+        <v>-28.790199081163</v>
       </c>
       <c r="I25" s="14">
-        <v>1644</v>
+        <v>1746</v>
       </c>
       <c r="J25" s="14">
-        <v>2299</v>
+        <v>2453</v>
       </c>
       <c r="K25" s="15">
-        <v>-28.490648107873</v>
+        <v>-28.821850794945</v>
       </c>
       <c r="L25" s="15">
-        <v>-40.477914554670</v>
+        <v>-40.551583248212</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D26" s="14">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E26" s="15">
-        <v>5.607476635514</v>
+        <v>17.821782178217</v>
       </c>
       <c r="F26" s="14">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="G26" s="14">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="H26" s="15">
-        <v>3.496503496503</v>
+        <v>7.529411764705</v>
       </c>
       <c r="I26" s="14">
-        <v>1285</v>
+        <v>1402</v>
       </c>
       <c r="J26" s="14">
-        <v>1327</v>
+        <v>1428</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.165033911077</v>
+        <v>-1.820728291316</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.046543463381</v>
+        <v>-10.757479312539</v>
       </c>
       <c r="M26" s="15">
-        <v>7.262103505843</v>
+        <v>8.766485647788</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D27" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E27" s="15">
-        <v>-60</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F27" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H27" s="15">
-        <v>-28</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="I27" s="14">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J27" s="14">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K27" s="15">
-        <v>2.631578947368</v>
+        <v>4.819277108433</v>
       </c>
       <c r="L27" s="15">
-        <v>14.705882352941</v>
+        <v>12.987012987013</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D28" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E28" s="15">
-        <v>58.333333333333</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G28" s="14">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H28" s="15">
-        <v>40.476190476190</v>
+        <v>74.285714285714</v>
       </c>
       <c r="I28" s="14">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="J28" s="14">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="K28" s="15">
-        <v>-3.597122302158</v>
+        <v>-0.689655172413</v>
       </c>
       <c r="L28" s="15">
-        <v>-6.944444444444</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="14">
+        <v>2</v>
+      </c>
+      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>28</v>
+      <c r="E29" s="15">
+        <v>100</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I29" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J29" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K29" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M29" s="15">
-        <v>-38.461538461538</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.235294117647</v>
+        <v>-85.507246376811</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>28</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
         <v>3</v>
@@ -1526,63 +1526,63 @@
         <v>50</v>
       </c>
       <c r="I30" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J30" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K30" s="15">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
       <c r="L30" s="15">
-        <v>166.666666666667</v>
+        <v>200</v>
       </c>
       <c r="M30" s="15">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.878787878787</v>
+        <v>-86.567164179104</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>3</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G31" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H31" s="15">
-        <v>33.333333333333</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I31" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J31" s="14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K31" s="15">
-        <v>44.444444444444</v>
+        <v>4.166666666666</v>
       </c>
       <c r="L31" s="15">
-        <v>18.181818181818</v>
+        <v>4.166666666666</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,23 +1607,23 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>2</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F33" s="14">
         <v>3</v>
       </c>
       <c r="G33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I33" s="14">
         <v>8</v>
@@ -1638,10 +1638,10 @@
         <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>218</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>10079</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>2992</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>17454</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>11614</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>28509</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>71017</v>

--- a/data/source/weekly/cs-en-us-pbqn.xlsx
+++ b/data/source/weekly/cs-en-us-pbqn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -861,22 +861,22 @@
         <v>-100</v>
       </c>
       <c r="F14" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="15">
-        <v>66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I14" s="14">
         <v>8</v>
       </c>
       <c r="J14" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L14" s="15">
         <v>100</v>
@@ -885,7 +885,7 @@
         <v>-20</v>
       </c>
       <c r="N14" s="15">
-        <v>-80</v>
+        <v>-80.952380952380</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G15" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H15" s="15">
-        <v>-30.434782608695</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J15" s="14">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K15" s="15">
-        <v>14.285714285714</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L15" s="15">
-        <v>46.938775510204</v>
+        <v>44.444444444444</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>110.810810810811</v>
       </c>
       <c r="N15" s="15">
-        <v>63.636363636363</v>
+        <v>73.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D16" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="15">
-        <v>26.923076923076</v>
+        <v>44</v>
       </c>
       <c r="F16" s="14">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G16" s="14">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H16" s="15">
-        <v>-11.940298507462</v>
+        <v>1.587301587301</v>
       </c>
       <c r="I16" s="14">
-        <v>379</v>
+        <v>415</v>
       </c>
       <c r="J16" s="14">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="K16" s="15">
-        <v>-4.292929292929</v>
+        <v>-1.425178147268</v>
       </c>
       <c r="L16" s="15">
-        <v>-34.879725085910</v>
+        <v>-34.022257551669</v>
       </c>
       <c r="M16" s="15">
-        <v>-27.671755725190</v>
+        <v>-25.760286225402</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.258654220147</v>
+        <v>-84.820775420629</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="D17" s="14">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="E17" s="15">
-        <v>-4.166666666666</v>
+        <v>15.151515151515</v>
       </c>
       <c r="F17" s="14">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="G17" s="14">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H17" s="15">
-        <v>5.607476635514</v>
+        <v>5.963302752293</v>
       </c>
       <c r="I17" s="14">
-        <v>735</v>
+        <v>814</v>
       </c>
       <c r="J17" s="14">
-        <v>824</v>
+        <v>890</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.800970873786</v>
+        <v>-8.539325842696</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.239700374531</v>
+        <v>-7.709750566893</v>
       </c>
       <c r="M17" s="15">
-        <v>85.138539042821</v>
+        <v>87.990762124711</v>
       </c>
       <c r="N17" s="15">
-        <v>5.150214592274</v>
+        <v>8.388814913448</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D18" s="14">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E18" s="15">
-        <v>-61.904761904761</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="F18" s="14">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G18" s="14">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="H18" s="15">
-        <v>-46.103896103896</v>
+        <v>-40.136054421768</v>
       </c>
       <c r="I18" s="14">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="J18" s="14">
-        <v>563</v>
+        <v>596</v>
       </c>
       <c r="K18" s="15">
-        <v>-40.319715808170</v>
+        <v>-38.590604026845</v>
       </c>
       <c r="L18" s="15">
-        <v>-39.350180505415</v>
+        <v>-38.590604026845</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.629255989911</v>
+        <v>-56.220095693779</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.041686404547</v>
+        <v>-91.859430604982</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="D19" s="14">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E19" s="15">
-        <v>-21.568627450980</v>
+        <v>0.909090909090</v>
       </c>
       <c r="F19" s="14">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="G19" s="14">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="H19" s="15">
-        <v>-8.695652173913</v>
+        <v>-12.925170068027</v>
       </c>
       <c r="I19" s="14">
-        <v>1488</v>
+        <v>1598</v>
       </c>
       <c r="J19" s="14">
-        <v>1450</v>
+        <v>1560</v>
       </c>
       <c r="K19" s="15">
-        <v>2.620689655172</v>
+        <v>2.435897435897</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.174361759913</v>
+        <v>-18.55249745158</v>
       </c>
       <c r="M19" s="15">
-        <v>38.805970149253</v>
+        <v>39.563318777292</v>
       </c>
       <c r="N19" s="15">
-        <v>-28.219971056439</v>
+        <v>-28.276481149012</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D20" s="14">
         <v>52</v>
       </c>
       <c r="E20" s="15">
-        <v>19.230769230769</v>
+        <v>26.923076923076</v>
       </c>
       <c r="F20" s="14">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="G20" s="14">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="H20" s="15">
-        <v>18.285714285714</v>
+        <v>20</v>
       </c>
       <c r="I20" s="14">
-        <v>643</v>
+        <v>710</v>
       </c>
       <c r="J20" s="14">
-        <v>522</v>
+        <v>574</v>
       </c>
       <c r="K20" s="15">
-        <v>23.180076628352</v>
+        <v>23.693379790940</v>
       </c>
       <c r="L20" s="15">
-        <v>0.783699059561</v>
+        <v>3.197674418604</v>
       </c>
       <c r="M20" s="15">
-        <v>35.084033613445</v>
+        <v>39.763779527559</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.163683646932</v>
+        <v>-89.900426742532</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>244</v>
+        <v>324</v>
       </c>
       <c r="D21" s="17">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.230215827338</v>
+        <v>11.724137931034</v>
       </c>
       <c r="F21" s="17">
-        <v>1033</v>
+        <v>1075</v>
       </c>
       <c r="G21" s="17">
-        <v>1117</v>
+        <v>1139</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.520143240823</v>
+        <v>-5.618964003511</v>
       </c>
       <c r="I21" s="17">
-        <v>3661</v>
+        <v>3989</v>
       </c>
       <c r="J21" s="17">
-        <v>3826</v>
+        <v>4116</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.312598013591</v>
+        <v>-3.085519922254</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.080107406578</v>
+        <v>-17.154724818276</v>
       </c>
       <c r="M21" s="18">
-        <v>10.671100362757</v>
+        <v>13.066893424036</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.381687878413</v>
+        <v>-76.976797876024</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>28</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22" s="14">
         <v>8</v>
       </c>
       <c r="E22" s="15">
-        <v>-87.5</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G22" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H22" s="15">
-        <v>-75.757575757575</v>
+        <v>-70.967741935483</v>
       </c>
       <c r="I22" s="14">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J22" s="14">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K22" s="15">
-        <v>-38.709677419354</v>
+        <v>-39.603960396039</v>
       </c>
       <c r="L22" s="15">
-        <v>-26.923076923076</v>
+        <v>-25.609756097561</v>
       </c>
       <c r="M22" s="15">
-        <v>3.636363636363</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>29</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F23" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G23" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H23" s="15">
-        <v>12.5</v>
+        <v>26.666666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J23" s="14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K23" s="15">
-        <v>-4.615384615384</v>
+        <v>-2.857142857142</v>
       </c>
       <c r="L23" s="15">
-        <v>3.333333333333</v>
+        <v>7.936507936507</v>
       </c>
       <c r="M23" s="15">
-        <v>47.619047619047</v>
+        <v>61.904761904761</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>29</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="D24" s="14">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="E24" s="15">
-        <v>-18.996415770609</v>
+        <v>4.8</v>
       </c>
       <c r="F24" s="14">
-        <v>985</v>
+        <v>950</v>
       </c>
       <c r="G24" s="14">
-        <v>1100</v>
+        <v>1084</v>
       </c>
       <c r="H24" s="15">
-        <v>-10.454545454545</v>
+        <v>-12.361623616236</v>
       </c>
       <c r="I24" s="14">
-        <v>3536</v>
+        <v>3797</v>
       </c>
       <c r="J24" s="14">
-        <v>3965</v>
+        <v>4215</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.819672131147</v>
+        <v>-9.916963226571</v>
       </c>
       <c r="L24" s="15">
-        <v>-24.136451405277</v>
+        <v>-23.416700282371</v>
       </c>
       <c r="M24" s="15">
-        <v>47.517730496453</v>
+        <v>47.628304821150</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>29</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="D25" s="14">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.116883116883</v>
+        <v>-8.633093525179</v>
       </c>
       <c r="F25" s="14">
-        <v>465</v>
+        <v>433</v>
       </c>
       <c r="G25" s="14">
-        <v>653</v>
+        <v>638</v>
       </c>
       <c r="H25" s="15">
-        <v>-28.790199081163</v>
+        <v>-32.131661442006</v>
       </c>
       <c r="I25" s="14">
-        <v>1746</v>
+        <v>1872</v>
       </c>
       <c r="J25" s="14">
-        <v>2453</v>
+        <v>2592</v>
       </c>
       <c r="K25" s="15">
-        <v>-28.821850794945</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="L25" s="15">
-        <v>-40.551583248212</v>
+        <v>-40.076824583866</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>29</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D26" s="14">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="E26" s="15">
-        <v>17.821782178217</v>
+        <v>-6.034482758620</v>
       </c>
       <c r="F26" s="14">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="G26" s="14">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H26" s="15">
-        <v>7.529411764705</v>
+        <v>5.700712589073</v>
       </c>
       <c r="I26" s="14">
-        <v>1402</v>
+        <v>1508</v>
       </c>
       <c r="J26" s="14">
-        <v>1428</v>
+        <v>1544</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.820728291316</v>
+        <v>-2.331606217616</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.757479312539</v>
+        <v>-10.874704491725</v>
       </c>
       <c r="M26" s="15">
-        <v>8.766485647788</v>
+        <v>8.959537572254</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>29</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E27" s="15">
-        <v>28.571428571428</v>
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G27" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H27" s="15">
-        <v>-32.142857142857</v>
+        <v>13.043478260869</v>
       </c>
       <c r="I27" s="14">
+        <v>95</v>
+      </c>
+      <c r="J27" s="14">
         <v>87</v>
       </c>
-      <c r="J27" s="14">
-        <v>83</v>
-      </c>
       <c r="K27" s="15">
-        <v>4.819277108433</v>
+        <v>9.195402298850</v>
       </c>
       <c r="L27" s="15">
-        <v>12.987012987013</v>
+        <v>13.095238095238</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>29</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D28" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E28" s="15">
-        <v>83.333333333333</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F28" s="14">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G28" s="14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H28" s="15">
-        <v>74.285714285714</v>
+        <v>82.352941176470</v>
       </c>
       <c r="I28" s="14">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="J28" s="14">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="K28" s="15">
-        <v>-0.689655172413</v>
+        <v>2.597402597402</v>
       </c>
       <c r="L28" s="15">
-        <v>-11.111111111111</v>
+        <v>-9.195402298850</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>29</v>
@@ -1466,23 +1466,23 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
-      </c>
-      <c r="D29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" s="14">
+        <v>3</v>
+      </c>
+      <c r="G29" s="14">
         <v>1</v>
       </c>
-      <c r="E29" s="15">
-        <v>100</v>
-      </c>
-      <c r="F29" s="14">
-        <v>4</v>
-      </c>
-      <c r="G29" s="14">
-        <v>2</v>
-      </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I29" s="14">
         <v>10</v>
@@ -1494,36 +1494,36 @@
         <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M29" s="15">
-        <v>-28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-85.507246376811</v>
+        <v>-86.301369863013</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30" s="14">
+        <v>2</v>
+      </c>
+      <c r="G30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
-      </c>
-      <c r="F30" s="14">
-        <v>3</v>
-      </c>
-      <c r="G30" s="14">
-        <v>2</v>
-      </c>
       <c r="H30" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
         <v>9</v>
@@ -1535,13 +1535,13 @@
         <v>-10</v>
       </c>
       <c r="L30" s="15">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="M30" s="15">
-        <v>-10</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N30" s="15">
-        <v>-86.567164179104</v>
+        <v>-87.323943661971</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1552,31 +1552,31 @@
         <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E31" s="15">
         <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G31" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H31" s="15">
-        <v>-53.846153846153</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="I31" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J31" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K31" s="15">
-        <v>4.166666666666</v>
+        <v>0</v>
       </c>
       <c r="L31" s="15">
-        <v>4.166666666666</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>29</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>29</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
         <v>3</v>
@@ -1629,13 +1629,13 @@
         <v>8</v>
       </c>
       <c r="J33" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33" s="15">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L33" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>29</v>

--- a/data/source/weekly/cs-en-us-pbqn.xlsx
+++ b/data/source/weekly/cs-en-us-pbqn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -855,7 +855,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="15">
         <v>-100</v>
@@ -864,19 +864,19 @@
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="I14" s="14">
         <v>8</v>
       </c>
       <c r="J14" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K14" s="15">
-        <v>-11.111111111111</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L14" s="15">
         <v>100</v>
@@ -893,40 +893,40 @@
         <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G15" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H15" s="15">
-        <v>16.666666666666</v>
+        <v>18.75</v>
       </c>
       <c r="I15" s="14">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J15" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K15" s="15">
-        <v>18.181818181818</v>
+        <v>17.142857142857</v>
       </c>
       <c r="L15" s="15">
-        <v>44.444444444444</v>
+        <v>43.859649122807</v>
       </c>
       <c r="M15" s="15">
-        <v>110.810810810811</v>
+        <v>115.789473684211</v>
       </c>
       <c r="N15" s="15">
-        <v>73.333333333333</v>
+        <v>60.784313725490</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D16" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E16" s="15">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G16" s="14">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H16" s="15">
-        <v>1.587301587301</v>
+        <v>5.833333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>415</v>
+        <v>446</v>
       </c>
       <c r="J16" s="14">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="K16" s="15">
-        <v>-1.425178147268</v>
+        <v>-1.108647450110</v>
       </c>
       <c r="L16" s="15">
-        <v>-34.022257551669</v>
+        <v>-33.729569093610</v>
       </c>
       <c r="M16" s="15">
-        <v>-25.760286225402</v>
+        <v>-23.499142367066</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.820775420629</v>
+        <v>-84.567474048442</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="D17" s="14">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E17" s="15">
-        <v>15.151515151515</v>
+        <v>-32</v>
       </c>
       <c r="F17" s="14">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G17" s="14">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="H17" s="15">
-        <v>5.963302752293</v>
+        <v>-9.126984126984</v>
       </c>
       <c r="I17" s="14">
-        <v>814</v>
+        <v>865</v>
       </c>
       <c r="J17" s="14">
-        <v>890</v>
+        <v>965</v>
       </c>
       <c r="K17" s="15">
-        <v>-8.539325842696</v>
+        <v>-10.362694300518</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.709750566893</v>
+        <v>-7.089151450053</v>
       </c>
       <c r="M17" s="15">
-        <v>87.990762124711</v>
+        <v>84.434968017057</v>
       </c>
       <c r="N17" s="15">
-        <v>8.388814913448</v>
+        <v>6.134969325153</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" s="14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" s="15">
-        <v>-12.121212121212</v>
+        <v>-12.5</v>
       </c>
       <c r="F18" s="14">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G18" s="14">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H18" s="15">
-        <v>-40.136054421768</v>
+        <v>-32.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="J18" s="14">
-        <v>596</v>
+        <v>628</v>
       </c>
       <c r="K18" s="15">
-        <v>-38.590604026845</v>
+        <v>-37.261146496815</v>
       </c>
       <c r="L18" s="15">
-        <v>-38.590604026845</v>
+        <v>-38.050314465408</v>
       </c>
       <c r="M18" s="15">
-        <v>-56.220095693779</v>
+        <v>-54.660529344073</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.859430604982</v>
+        <v>-91.713985278654</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D19" s="14">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E19" s="15">
-        <v>0.909090909090</v>
+        <v>24.742268041237</v>
       </c>
       <c r="F19" s="14">
-        <v>384</v>
+        <v>419</v>
       </c>
       <c r="G19" s="14">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="H19" s="15">
-        <v>-12.925170068027</v>
+        <v>-0.710900473933</v>
       </c>
       <c r="I19" s="14">
-        <v>1598</v>
+        <v>1721</v>
       </c>
       <c r="J19" s="14">
-        <v>1560</v>
+        <v>1657</v>
       </c>
       <c r="K19" s="15">
-        <v>2.435897435897</v>
+        <v>3.862401931200</v>
       </c>
       <c r="L19" s="15">
-        <v>-18.55249745158</v>
+        <v>-17.969494756911</v>
       </c>
       <c r="M19" s="15">
-        <v>39.563318777292</v>
+        <v>42.113955408753</v>
       </c>
       <c r="N19" s="15">
-        <v>-28.276481149012</v>
+        <v>-27.414592998734</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D20" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E20" s="15">
-        <v>26.923076923076</v>
+        <v>1.851851851851</v>
       </c>
       <c r="F20" s="14">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="G20" s="14">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="H20" s="15">
-        <v>20</v>
+        <v>18.686868686868</v>
       </c>
       <c r="I20" s="14">
-        <v>710</v>
+        <v>764</v>
       </c>
       <c r="J20" s="14">
-        <v>574</v>
+        <v>628</v>
       </c>
       <c r="K20" s="15">
-        <v>23.693379790940</v>
+        <v>21.656050955414</v>
       </c>
       <c r="L20" s="15">
-        <v>3.197674418604</v>
+        <v>3.663500678426</v>
       </c>
       <c r="M20" s="15">
-        <v>39.763779527559</v>
+        <v>38.656987295825</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.900426742532</v>
+        <v>-89.758713136729</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>324</v>
+        <v>289</v>
       </c>
       <c r="D21" s="17">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E21" s="18">
-        <v>11.724137931034</v>
+        <v>-1.700680272108</v>
       </c>
       <c r="F21" s="17">
-        <v>1075</v>
+        <v>1124</v>
       </c>
       <c r="G21" s="17">
-        <v>1139</v>
+        <v>1153</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.618964003511</v>
+        <v>-2.515177797051</v>
       </c>
       <c r="I21" s="17">
-        <v>3989</v>
+        <v>4280</v>
       </c>
       <c r="J21" s="17">
-        <v>4116</v>
+        <v>4410</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.085519922254</v>
+        <v>-2.947845804988</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.154724818276</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M21" s="18">
-        <v>13.066893424036</v>
+        <v>14.714553738944</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.976797876024</v>
+        <v>-76.718885987815</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>28</v>
       </c>
       <c r="C22" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E22" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="F22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H22" s="15">
-        <v>-70.967741935483</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J22" s="14">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="K22" s="15">
-        <v>-39.603960396039</v>
+        <v>-40.566037735849</v>
       </c>
       <c r="L22" s="15">
-        <v>-25.609756097561</v>
+        <v>-24.096385542168</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-3.076923076923</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>29</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G23" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H23" s="15">
-        <v>26.666666666666</v>
+        <v>-6.25</v>
       </c>
       <c r="I23" s="14">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J23" s="14">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K23" s="15">
-        <v>-2.857142857142</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="L23" s="15">
-        <v>7.936507936507</v>
+        <v>2.941176470588</v>
       </c>
       <c r="M23" s="15">
-        <v>61.904761904761</v>
+        <v>52.173913043478</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>29</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D24" s="14">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="E24" s="15">
-        <v>4.8</v>
+        <v>11.618257261410</v>
       </c>
       <c r="F24" s="14">
-        <v>950</v>
+        <v>961</v>
       </c>
       <c r="G24" s="14">
-        <v>1084</v>
+        <v>1047</v>
       </c>
       <c r="H24" s="15">
-        <v>-12.361623616236</v>
+        <v>-8.213944603629</v>
       </c>
       <c r="I24" s="14">
-        <v>3797</v>
+        <v>4063</v>
       </c>
       <c r="J24" s="14">
-        <v>4215</v>
+        <v>4456</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.916963226571</v>
+        <v>-8.819569120287</v>
       </c>
       <c r="L24" s="15">
-        <v>-23.416700282371</v>
+        <v>-22.668443090978</v>
       </c>
       <c r="M24" s="15">
-        <v>47.628304821150</v>
+        <v>46.203670385030</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>29</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D25" s="14">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E25" s="15">
-        <v>-8.633093525179</v>
+        <v>-4.861111111111</v>
       </c>
       <c r="F25" s="14">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="G25" s="14">
-        <v>638</v>
+        <v>603</v>
       </c>
       <c r="H25" s="15">
-        <v>-32.131661442006</v>
+        <v>-25.704809286898</v>
       </c>
       <c r="I25" s="14">
-        <v>1872</v>
+        <v>2010</v>
       </c>
       <c r="J25" s="14">
-        <v>2592</v>
+        <v>2736</v>
       </c>
       <c r="K25" s="15">
-        <v>-27.777777777777</v>
+        <v>-26.535087719298</v>
       </c>
       <c r="L25" s="15">
-        <v>-40.076824583866</v>
+        <v>-39.403075067832</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>29</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="D26" s="14">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E26" s="15">
-        <v>-6.034482758620</v>
+        <v>-19.298245614035</v>
       </c>
       <c r="F26" s="14">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="G26" s="14">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="H26" s="15">
-        <v>5.700712589073</v>
+        <v>-1.369863013698</v>
       </c>
       <c r="I26" s="14">
-        <v>1508</v>
+        <v>1599</v>
       </c>
       <c r="J26" s="14">
-        <v>1544</v>
+        <v>1658</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.331606217616</v>
+        <v>-3.558504221954</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.874704491725</v>
+        <v>-11.803640375068</v>
       </c>
       <c r="M26" s="15">
-        <v>8.959537572254</v>
+        <v>8.701563562202</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>29</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27" s="14">
         <v>4</v>
       </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F27" s="14">
         <v>26</v>
       </c>
       <c r="G27" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H27" s="15">
-        <v>13.043478260869</v>
+        <v>30</v>
       </c>
       <c r="I27" s="14">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J27" s="14">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K27" s="15">
-        <v>9.195402298850</v>
+        <v>12.087912087912</v>
       </c>
       <c r="L27" s="15">
-        <v>13.095238095238</v>
+        <v>15.909090909090</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>29</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D28" s="14">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E28" s="15">
-        <v>55.555555555555</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F28" s="14">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G28" s="14">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H28" s="15">
-        <v>82.352941176470</v>
+        <v>22.727272727272</v>
       </c>
       <c r="I28" s="14">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="J28" s="14">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="K28" s="15">
-        <v>2.597402597402</v>
+        <v>-1.169590643274</v>
       </c>
       <c r="L28" s="15">
-        <v>-9.195402298850</v>
+        <v>-10.582010582010</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>29</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>29</v>
+      <c r="C29" s="14">
+        <v>4</v>
+      </c>
+      <c r="D29" s="14">
+        <v>3</v>
+      </c>
+      <c r="E29" s="15">
+        <v>33.333333333333</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="I29" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J29" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L29" s="15">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="M29" s="15">
-        <v>-33.333333333333</v>
+        <v>-12.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-86.301369863013</v>
+        <v>-81.578947368421</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>29</v>
+      <c r="C30" s="14">
+        <v>2</v>
+      </c>
+      <c r="D30" s="14">
+        <v>3</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J30" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K30" s="15">
-        <v>-10</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L30" s="15">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="M30" s="15">
-        <v>-18.181818181818</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.323943661971</v>
+        <v>-85.135135135135</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1552,7 +1552,7 @@
         <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E31" s="15">
         <v>-100</v>
@@ -1561,22 +1561,22 @@
         <v>4</v>
       </c>
       <c r="G31" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H31" s="15">
-        <v>-73.333333333333</v>
+        <v>-78.947368421052</v>
       </c>
       <c r="I31" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J31" s="14">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K31" s="15">
-        <v>0</v>
+        <v>-20.588235294117</v>
       </c>
       <c r="L31" s="15">
-        <v>8.333333333333</v>
+        <v>12.5</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>29</v>
@@ -1607,35 +1607,35 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="14">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="E33" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F33" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I33" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J33" s="14">
         <v>6</v>
       </c>
       <c r="K33" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="L33" s="15">
-        <v>-55.555555555555</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>29</v>

--- a/data/source/weekly/cs-en-us-pbqn.xlsx
+++ b/data/source/weekly/cs-en-us-pbqn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,20 +854,20 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>2</v>
-      </c>
-      <c r="E14" s="15">
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="15">
         <v>-100</v>
-      </c>
-      <c r="F14" s="14">
-        <v>1</v>
-      </c>
-      <c r="G14" s="14">
-        <v>5</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-80</v>
       </c>
       <c r="I14" s="14">
         <v>8</v>
@@ -879,341 +879,341 @@
         <v>-27.272727272727</v>
       </c>
       <c r="L14" s="15">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="M14" s="15">
         <v>-20</v>
       </c>
       <c r="N14" s="15">
-        <v>-80.952380952380</v>
+        <v>-81.395348837209</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F15" s="14">
+        <v>25</v>
+      </c>
+      <c r="G15" s="14">
         <v>19</v>
       </c>
-      <c r="G15" s="14">
-        <v>16</v>
-      </c>
       <c r="H15" s="15">
-        <v>18.75</v>
+        <v>31.578947368421</v>
       </c>
       <c r="I15" s="14">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J15" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K15" s="15">
-        <v>17.142857142857</v>
+        <v>20</v>
       </c>
       <c r="L15" s="15">
-        <v>43.859649122807</v>
+        <v>55.172413793103</v>
       </c>
       <c r="M15" s="15">
-        <v>115.789473684211</v>
+        <v>125</v>
       </c>
       <c r="N15" s="15">
-        <v>60.784313725490</v>
+        <v>52.542372881355</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D16" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F16" s="14">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G16" s="14">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H16" s="15">
-        <v>5.833333333333</v>
+        <v>12.820512820512</v>
       </c>
       <c r="I16" s="14">
-        <v>446</v>
+        <v>480</v>
       </c>
       <c r="J16" s="14">
-        <v>451</v>
+        <v>487</v>
       </c>
       <c r="K16" s="15">
-        <v>-1.108647450110</v>
+        <v>-1.437371663244</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.729569093610</v>
+        <v>-32.584269662921</v>
       </c>
       <c r="M16" s="15">
-        <v>-23.499142367066</v>
+        <v>-21.440261865793</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.567474048442</v>
+        <v>-84.405458089668</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D17" s="14">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E17" s="15">
-        <v>-32</v>
+        <v>-28.947368421052</v>
       </c>
       <c r="F17" s="14">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G17" s="14">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="H17" s="15">
-        <v>-9.126984126984</v>
+        <v>-13.962264150943</v>
       </c>
       <c r="I17" s="14">
-        <v>865</v>
+        <v>919</v>
       </c>
       <c r="J17" s="14">
-        <v>965</v>
+        <v>1041</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.362694300518</v>
+        <v>-11.719500480307</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.089151450053</v>
+        <v>-7.730923694779</v>
       </c>
       <c r="M17" s="15">
-        <v>84.434968017057</v>
+        <v>82.341269841269</v>
       </c>
       <c r="N17" s="15">
-        <v>6.134969325153</v>
+        <v>4.313280363223</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D18" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E18" s="15">
-        <v>-12.5</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G18" s="14">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H18" s="15">
-        <v>-32.857142857142</v>
+        <v>-36.551724137931</v>
       </c>
       <c r="I18" s="14">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="J18" s="14">
-        <v>628</v>
+        <v>666</v>
       </c>
       <c r="K18" s="15">
-        <v>-37.261146496815</v>
+        <v>-37.987987987988</v>
       </c>
       <c r="L18" s="15">
-        <v>-38.050314465408</v>
+        <v>-38.450074515648</v>
       </c>
       <c r="M18" s="15">
-        <v>-54.660529344073</v>
+        <v>-55.157437567861</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.713985278654</v>
+        <v>-91.774546903007</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="D19" s="14">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="E19" s="15">
-        <v>24.742268041237</v>
+        <v>-9.009009009009</v>
       </c>
       <c r="F19" s="14">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G19" s="14">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H19" s="15">
-        <v>-0.710900473933</v>
+        <v>-0.714285714285</v>
       </c>
       <c r="I19" s="14">
-        <v>1721</v>
+        <v>1827</v>
       </c>
       <c r="J19" s="14">
-        <v>1657</v>
+        <v>1768</v>
       </c>
       <c r="K19" s="15">
-        <v>3.862401931200</v>
+        <v>3.337104072398</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.969494756911</v>
+        <v>-18.328118015198</v>
       </c>
       <c r="M19" s="15">
-        <v>42.113955408753</v>
+        <v>42.957746478873</v>
       </c>
       <c r="N19" s="15">
-        <v>-27.414592998734</v>
+        <v>-27.586206896551</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D20" s="14">
         <v>54</v>
       </c>
       <c r="E20" s="15">
-        <v>1.851851851851</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="G20" s="14">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="H20" s="15">
-        <v>18.686868686868</v>
+        <v>6.132075471698</v>
       </c>
       <c r="I20" s="14">
-        <v>764</v>
+        <v>806</v>
       </c>
       <c r="J20" s="14">
-        <v>628</v>
+        <v>682</v>
       </c>
       <c r="K20" s="15">
-        <v>21.656050955414</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L20" s="15">
-        <v>3.663500678426</v>
+        <v>3.865979381443</v>
       </c>
       <c r="M20" s="15">
-        <v>38.656987295825</v>
+        <v>37.308347529812</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.758713136729</v>
+        <v>-89.838628340897</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="D21" s="17">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="E21" s="18">
-        <v>-1.700680272108</v>
+        <v>-18.75</v>
       </c>
       <c r="F21" s="17">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="G21" s="17">
-        <v>1153</v>
+        <v>1182</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.515177797051</v>
+        <v>-5.329949238578</v>
       </c>
       <c r="I21" s="17">
-        <v>4280</v>
+        <v>4543</v>
       </c>
       <c r="J21" s="17">
-        <v>4410</v>
+        <v>4730</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.947845804988</v>
+        <v>-3.953488372093</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.666666666666</v>
+        <v>-16.718606782768</v>
       </c>
       <c r="M21" s="18">
-        <v>14.714553738944</v>
+        <v>14.983548468742</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.718885987815</v>
+        <v>-76.746685775707</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D22" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E22" s="15">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G22" s="14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H22" s="15">
-        <v>-66.666666666666</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="I22" s="14">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J22" s="14">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="K22" s="15">
-        <v>-40.566037735849</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="L22" s="15">
-        <v>-24.096385542168</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M22" s="15">
-        <v>-3.076923076923</v>
+        <v>9.090909090909</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>40</v>
       </c>
       <c r="F23" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G23" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H23" s="15">
-        <v>-6.25</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I23" s="14">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J23" s="14">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K23" s="15">
-        <v>-5.405405405405</v>
+        <v>-2.531645569620</v>
       </c>
       <c r="L23" s="15">
-        <v>2.941176470588</v>
+        <v>4.054054054054</v>
       </c>
       <c r="M23" s="15">
-        <v>52.173913043478</v>
+        <v>67.391304347826</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="D24" s="14">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="E24" s="15">
-        <v>11.618257261410</v>
+        <v>-12.056737588652</v>
       </c>
       <c r="F24" s="14">
-        <v>961</v>
+        <v>1002</v>
       </c>
       <c r="G24" s="14">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.213944603629</v>
+        <v>-4.752851711026</v>
       </c>
       <c r="I24" s="14">
-        <v>4063</v>
+        <v>4308</v>
       </c>
       <c r="J24" s="14">
-        <v>4456</v>
+        <v>4738</v>
       </c>
       <c r="K24" s="15">
-        <v>-8.819569120287</v>
+        <v>-9.075559307724</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.668443090978</v>
+        <v>-22.182080924855</v>
       </c>
       <c r="M24" s="15">
-        <v>46.203670385030</v>
+        <v>44.904137235116</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="D25" s="14">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E25" s="15">
-        <v>-4.861111111111</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="F25" s="14">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="G25" s="14">
-        <v>603</v>
+        <v>577</v>
       </c>
       <c r="H25" s="15">
-        <v>-25.704809286898</v>
+        <v>-17.677642980935</v>
       </c>
       <c r="I25" s="14">
-        <v>2010</v>
+        <v>2118</v>
       </c>
       <c r="J25" s="14">
-        <v>2736</v>
+        <v>2876</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.535087719298</v>
+        <v>-26.356050069541</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.403075067832</v>
+        <v>-39.225251076040</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D26" s="14">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E26" s="15">
-        <v>-19.298245614035</v>
+        <v>-3.539823008849</v>
       </c>
       <c r="F26" s="14">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="G26" s="14">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="H26" s="15">
-        <v>-1.369863013698</v>
+        <v>-3.828828828828</v>
       </c>
       <c r="I26" s="14">
-        <v>1599</v>
+        <v>1708</v>
       </c>
       <c r="J26" s="14">
-        <v>1658</v>
+        <v>1771</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.558504221954</v>
+        <v>-3.557312252964</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.803640375068</v>
+        <v>-12.723556463975</v>
       </c>
       <c r="M26" s="15">
-        <v>8.701563562202</v>
+        <v>8.651399491094</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G27" s="14">
         <v>20</v>
       </c>
       <c r="H27" s="15">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="I27" s="14">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="J27" s="14">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K27" s="15">
-        <v>12.087912087912</v>
+        <v>17.708333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>15.909090909090</v>
+        <v>20.212765957446</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,72 +1426,72 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D28" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E28" s="15">
-        <v>-29.411764705882</v>
+        <v>35.714285714285</v>
       </c>
       <c r="F28" s="14">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G28" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H28" s="15">
-        <v>22.727272727272</v>
+        <v>19.565217391304</v>
       </c>
       <c r="I28" s="14">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="J28" s="14">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="K28" s="15">
-        <v>-1.169590643274</v>
+        <v>1.621621621621</v>
       </c>
       <c r="L28" s="15">
-        <v>-10.582010582010</v>
+        <v>-2.590673575129</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>4</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" s="15">
-        <v>33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H29" s="15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>14</v>
       </c>
       <c r="J29" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K29" s="15">
-        <v>7.692307692307</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L29" s="15">
         <v>180</v>
@@ -1500,39 +1500,39 @@
         <v>-12.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-81.578947368421</v>
+        <v>-83.529411764705</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
         <v>2</v>
       </c>
-      <c r="D30" s="14">
+      <c r="E30" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F30" s="14">
         <v>3</v>
       </c>
-      <c r="E30" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F30" s="14">
-        <v>4</v>
-      </c>
       <c r="G30" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
         <v>11</v>
       </c>
       <c r="J30" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K30" s="15">
-        <v>-15.384615384615</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="L30" s="15">
         <v>175</v>
@@ -1541,7 +1541,7 @@
         <v>-8.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-85.135135135135</v>
+        <v>-86.585365853658</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1552,37 +1552,37 @@
         <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E31" s="15">
         <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H31" s="15">
-        <v>-78.947368421052</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="I31" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J31" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K31" s="15">
-        <v>-20.588235294117</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L31" s="15">
-        <v>12.5</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,41 +1607,41 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I33" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J33" s="14">
         <v>6</v>
       </c>
       <c r="K33" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L33" s="15">
-        <v>-52.631578947368</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>218</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>10079</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>2992</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>17454</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>11614</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>28509</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>71017</v>

--- a/data/source/weekly/cs-en-us-pbqn.xlsx
+++ b/data/source/weekly/cs-en-us-pbqn.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>2</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -873,347 +873,347 @@
         <v>8</v>
       </c>
       <c r="J14" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K14" s="15">
-        <v>-27.272727272727</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L14" s="15">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M14" s="15">
         <v>-20</v>
       </c>
       <c r="N14" s="15">
-        <v>-81.395348837209</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" s="14">
         <v>5</v>
       </c>
       <c r="E15" s="15">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F15" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G15" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H15" s="15">
-        <v>31.578947368421</v>
+        <v>41.176470588235</v>
       </c>
       <c r="I15" s="14">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J15" s="14">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K15" s="15">
         <v>20</v>
       </c>
       <c r="L15" s="15">
-        <v>55.172413793103</v>
+        <v>52.380952380952</v>
       </c>
       <c r="M15" s="15">
-        <v>125</v>
+        <v>134.146341463415</v>
       </c>
       <c r="N15" s="15">
-        <v>52.542372881355</v>
+        <v>54.838709677419</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" s="14">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E16" s="15">
-        <v>-5.555555555555</v>
+        <v>13.793103448275</v>
       </c>
       <c r="F16" s="14">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G16" s="14">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H16" s="15">
-        <v>12.820512820512</v>
+        <v>10.833333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>480</v>
+        <v>512</v>
       </c>
       <c r="J16" s="14">
-        <v>487</v>
+        <v>516</v>
       </c>
       <c r="K16" s="15">
-        <v>-1.437371663244</v>
+        <v>-0.775193798449</v>
       </c>
       <c r="L16" s="15">
-        <v>-32.584269662921</v>
+        <v>-32.095490716180</v>
       </c>
       <c r="M16" s="15">
-        <v>-21.440261865793</v>
+        <v>-20.496894409937</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.405458089668</v>
+        <v>-84.289659404725</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" s="14">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E17" s="15">
-        <v>-28.947368421052</v>
+        <v>-9.836065573770</v>
       </c>
       <c r="F17" s="14">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="G17" s="14">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="H17" s="15">
-        <v>-13.962264150943</v>
+        <v>-14.028776978417</v>
       </c>
       <c r="I17" s="14">
-        <v>919</v>
+        <v>977</v>
       </c>
       <c r="J17" s="14">
-        <v>1041</v>
+        <v>1102</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.719500480307</v>
+        <v>-11.343012704174</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.730923694779</v>
+        <v>-7.040913415794</v>
       </c>
       <c r="M17" s="15">
-        <v>82.341269841269</v>
+        <v>86.095238095238</v>
       </c>
       <c r="N17" s="15">
-        <v>4.313280363223</v>
+        <v>2.303664921465</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="14">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>19</v>
-      </c>
       <c r="D18" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="F18" s="14">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="G18" s="14">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H18" s="15">
-        <v>-36.551724137931</v>
+        <v>-27.464788732394</v>
       </c>
       <c r="I18" s="14">
-        <v>413</v>
+        <v>440</v>
       </c>
       <c r="J18" s="14">
-        <v>666</v>
+        <v>705</v>
       </c>
       <c r="K18" s="15">
-        <v>-37.987987987988</v>
+        <v>-37.588652482269</v>
       </c>
       <c r="L18" s="15">
-        <v>-38.450074515648</v>
+        <v>-36.416184971098</v>
       </c>
       <c r="M18" s="15">
-        <v>-55.157437567861</v>
+        <v>-54.498448810754</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.774546903007</v>
+        <v>-91.665088084864</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="D19" s="14">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E19" s="15">
-        <v>-9.009009009009</v>
+        <v>-26.890756302521</v>
       </c>
       <c r="F19" s="14">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G19" s="14">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="H19" s="15">
-        <v>-0.714285714285</v>
+        <v>-3.890160183066</v>
       </c>
       <c r="I19" s="14">
-        <v>1827</v>
+        <v>1915</v>
       </c>
       <c r="J19" s="14">
-        <v>1768</v>
+        <v>1887</v>
       </c>
       <c r="K19" s="15">
-        <v>3.337104072398</v>
+        <v>1.483836777954</v>
       </c>
       <c r="L19" s="15">
-        <v>-18.328118015198</v>
+        <v>-18.855932203389</v>
       </c>
       <c r="M19" s="15">
-        <v>42.957746478873</v>
+        <v>40.912435614422</v>
       </c>
       <c r="N19" s="15">
-        <v>-27.586206896551</v>
+        <v>-28.942486085343</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="D20" s="14">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E20" s="15">
-        <v>-16.666666666666</v>
+        <v>53.488372093023</v>
       </c>
       <c r="F20" s="14">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G20" s="14">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="H20" s="15">
-        <v>6.132075471698</v>
+        <v>12.315270935960</v>
       </c>
       <c r="I20" s="14">
-        <v>806</v>
+        <v>871</v>
       </c>
       <c r="J20" s="14">
-        <v>682</v>
+        <v>725</v>
       </c>
       <c r="K20" s="15">
-        <v>18.181818181818</v>
+        <v>20.137931034482</v>
       </c>
       <c r="L20" s="15">
-        <v>3.865979381443</v>
+        <v>4.939759036144</v>
       </c>
       <c r="M20" s="15">
-        <v>37.308347529812</v>
+        <v>42.088091353996</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.838628340897</v>
+        <v>-89.575104727708</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="D21" s="17">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="E21" s="18">
-        <v>-18.75</v>
+        <v>-8.724832214765</v>
       </c>
       <c r="F21" s="17">
-        <v>1119</v>
+        <v>1147</v>
       </c>
       <c r="G21" s="17">
-        <v>1182</v>
+        <v>1202</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.329949238578</v>
+        <v>-4.575707154742</v>
       </c>
       <c r="I21" s="17">
-        <v>4543</v>
+        <v>4819</v>
       </c>
       <c r="J21" s="17">
-        <v>4730</v>
+        <v>5028</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.953488372093</v>
+        <v>-4.156722354813</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.718606782768</v>
+        <v>-16.278665740097</v>
       </c>
       <c r="M21" s="18">
-        <v>14.983548468742</v>
+        <v>15.869199326761</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.746685775707</v>
+        <v>-76.666828063719</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="14">
+        <v>4</v>
+      </c>
+      <c r="D22" s="14">
+        <v>10</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-60</v>
+      </c>
+      <c r="F22" s="14">
+        <v>18</v>
+      </c>
+      <c r="G22" s="14">
+        <v>31</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-41.935483870967</v>
+      </c>
+      <c r="I22" s="14">
+        <v>75</v>
+      </c>
+      <c r="J22" s="14">
+        <v>124</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-39.516129032258</v>
+      </c>
+      <c r="L22" s="15">
+        <v>-23.469387755102</v>
+      </c>
+      <c r="M22" s="15">
+        <v>7.142857142857</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="C22" s="14">
-        <v>8</v>
-      </c>
-      <c r="D22" s="14">
-        <v>8</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
-      </c>
-      <c r="F22" s="14">
-        <v>16</v>
-      </c>
-      <c r="G22" s="14">
-        <v>29</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-44.827586206896</v>
-      </c>
-      <c r="I22" s="14">
-        <v>72</v>
-      </c>
-      <c r="J22" s="14">
-        <v>114</v>
-      </c>
-      <c r="K22" s="15">
-        <v>-36.842105263157</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-18.181818181818</v>
-      </c>
-      <c r="M22" s="15">
-        <v>9.090909090909</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G23" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H23" s="15">
-        <v>5.555555555555</v>
+        <v>6.666666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J23" s="14">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K23" s="15">
-        <v>-2.531645569620</v>
+        <v>-2.5</v>
       </c>
       <c r="L23" s="15">
-        <v>4.054054054054</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="M23" s="15">
-        <v>67.391304347826</v>
+        <v>59.183673469387</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D24" s="14">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="E24" s="15">
-        <v>-12.056737588652</v>
+        <v>-11.070110701107</v>
       </c>
       <c r="F24" s="14">
-        <v>1002</v>
+        <v>1013</v>
       </c>
       <c r="G24" s="14">
-        <v>1052</v>
+        <v>1044</v>
       </c>
       <c r="H24" s="15">
-        <v>-4.752851711026</v>
+        <v>-2.969348659003</v>
       </c>
       <c r="I24" s="14">
-        <v>4308</v>
+        <v>4539</v>
       </c>
       <c r="J24" s="14">
-        <v>4738</v>
+        <v>5009</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.075559307724</v>
+        <v>-9.383110401277</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.182080924855</v>
+        <v>-21.795313576843</v>
       </c>
       <c r="M24" s="15">
-        <v>44.904137235116</v>
+        <v>44.692381255977</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D25" s="14">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E25" s="15">
-        <v>-25.714285714285</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F25" s="14">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="G25" s="14">
         <v>577</v>
       </c>
       <c r="H25" s="15">
-        <v>-17.677642980935</v>
+        <v>-15.771230502599</v>
       </c>
       <c r="I25" s="14">
-        <v>2118</v>
+        <v>2230</v>
       </c>
       <c r="J25" s="14">
-        <v>2876</v>
+        <v>3030</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.356050069541</v>
+        <v>-26.402640264026</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.225251076040</v>
+        <v>-38.482758620689</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D26" s="14">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E26" s="15">
-        <v>-3.539823008849</v>
+        <v>20.202020202020</v>
       </c>
       <c r="F26" s="14">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G26" s="14">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H26" s="15">
-        <v>-3.828828828828</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="I26" s="14">
-        <v>1708</v>
+        <v>1828</v>
       </c>
       <c r="J26" s="14">
-        <v>1771</v>
+        <v>1870</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.557312252964</v>
+        <v>-2.245989304812</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.723556463975</v>
+        <v>-12.619502868068</v>
       </c>
       <c r="M26" s="15">
-        <v>8.651399491094</v>
+        <v>9.789789789789</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G27" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H27" s="15">
-        <v>75</v>
+        <v>63.157894736842</v>
       </c>
       <c r="I27" s="14">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J27" s="14">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K27" s="15">
-        <v>17.708333333333</v>
+        <v>15.686274509803</v>
       </c>
       <c r="L27" s="15">
-        <v>20.212765957446</v>
+        <v>15.686274509803</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,163 +1426,163 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D28" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E28" s="15">
-        <v>35.714285714285</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F28" s="14">
+        <v>59</v>
+      </c>
+      <c r="G28" s="14">
         <v>55</v>
       </c>
-      <c r="G28" s="14">
-        <v>46</v>
-      </c>
       <c r="H28" s="15">
-        <v>19.565217391304</v>
+        <v>7.272727272727</v>
       </c>
       <c r="I28" s="14">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="J28" s="14">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="K28" s="15">
-        <v>1.621621621621</v>
+        <v>1.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-2.590673575129</v>
+        <v>-1.456310679611</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="E29" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F29" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G29" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H29" s="15">
         <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J29" s="14">
         <v>15</v>
       </c>
       <c r="K29" s="15">
-        <v>-6.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="M29" s="15">
-        <v>-12.5</v>
+        <v>-6.25</v>
       </c>
       <c r="N29" s="15">
-        <v>-83.529411764705</v>
+        <v>-83.146067415730</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="E30" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F30" s="14">
         <v>3</v>
       </c>
       <c r="G30" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="I30" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J30" s="14">
         <v>15</v>
       </c>
       <c r="K30" s="15">
-        <v>-26.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="L30" s="15">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="M30" s="15">
-        <v>-8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-86.585365853658</v>
+        <v>-85.882352941176</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="14">
+        <v>6</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="E31" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F31" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G31" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H31" s="15">
-        <v>-70.588235294117</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J31" s="14">
         <v>35</v>
       </c>
       <c r="K31" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L31" s="15">
-        <v>11.111111111111</v>
+        <v>20.689655172413</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,34 +1614,34 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I33" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J33" s="14">
         <v>6</v>
       </c>
       <c r="K33" s="15">
-        <v>66.666666666666</v>
+        <v>83.333333333333</v>
       </c>
       <c r="L33" s="15">
-        <v>-47.368421052631</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>218</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>10079</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>2992</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>17454</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>11614</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>28509</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>71017</v>
